--- a/frequencies.xlsx
+++ b/frequencies.xlsx
@@ -445,13 +445,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-3.747902519535273e-05</v>
+        <v>-0.1840952336788177</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.008647283539175987</v>
+        <v>0.007535470183938742</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.003870989428833127</v>
+        <v>-0.02231810241937637</v>
       </c>
     </row>
     <row r="3">
@@ -461,13 +461,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.005371306091547012</v>
+        <v>0.03192802891135216</v>
       </c>
       <c r="C3" t="n">
-        <v>0.005117314402014017</v>
+        <v>-0.0001036008034134284</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.001331186504103243</v>
+        <v>-0.003219404956325889</v>
       </c>
     </row>
     <row r="4">
@@ -477,13 +477,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001443393179215491</v>
+        <v>0.1225029155611992</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001576325739733875</v>
+        <v>-0.005605622194707394</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001460436498746276</v>
+        <v>0.006694207899272442</v>
       </c>
     </row>
     <row r="5">
@@ -493,13 +493,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.009938647039234638</v>
+        <v>-0.146861732006073</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.008679596707224846</v>
+        <v>0.00365769281052053</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001955067040398717</v>
+        <v>0.06988939642906189</v>
       </c>
     </row>
     <row r="6">
@@ -509,13 +509,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.0002355298493057489</v>
+        <v>-0.0381476990878582</v>
       </c>
       <c r="C6" t="n">
-        <v>0.004875684157013893</v>
+        <v>0.0009215770987793803</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002127162646502256</v>
+        <v>0.002930273301899433</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.003181406296789646</v>
+        <v>-0.166102796792984</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.003710661083459854</v>
+        <v>0.006128130480647087</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.003609787905588746</v>
+        <v>-0.05391233414411545</v>
       </c>
     </row>
     <row r="8">
@@ -541,13 +541,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0002313170552952215</v>
+        <v>0.1595820486545563</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.008281913585960865</v>
+        <v>-0.005823531188070774</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.00342185003682971</v>
+        <v>0.06124323979020119</v>
       </c>
     </row>
     <row r="9">
@@ -557,13 +557,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.07939638942480087</v>
+        <v>0.147405743598938</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.007571140304207802</v>
+        <v>-0.002847629599273205</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03078645095229149</v>
+        <v>-0.1003423482179642</v>
       </c>
     </row>
     <row r="10">
@@ -573,13 +573,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.003947819583117962</v>
+        <v>0.08968954533338547</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.008397810161113739</v>
+        <v>-0.003184733679518104</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.006055161356925964</v>
+        <v>-0.03963819891214371</v>
       </c>
     </row>
     <row r="11">
@@ -589,13 +589,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.008154201321303844</v>
+        <v>-0.1180892735719681</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0121162012219429</v>
+        <v>0.005898165516555309</v>
       </c>
       <c r="D11" t="n">
-        <v>0.001106529263779521</v>
+        <v>0.0002628120710141957</v>
       </c>
     </row>
     <row r="12">
@@ -605,13 +605,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.002773100743070245</v>
+        <v>0.08295014500617981</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.00960511714220047</v>
+        <v>-0.003907333593815565</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.006026240531355143</v>
+        <v>0.002753861248493195</v>
       </c>
     </row>
     <row r="13">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0002375924377702177</v>
+        <v>0.1383734345436096</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.006020836066454649</v>
+        <v>-0.005764704663306475</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.002574785612523556</v>
+        <v>0.02785073406994343</v>
       </c>
     </row>
     <row r="14">
@@ -637,13 +637,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.007289424072951078</v>
+        <v>-0.003365649376064539</v>
       </c>
       <c r="C14" t="n">
-        <v>0.01283342018723488</v>
+        <v>0.0009918769355863333</v>
       </c>
       <c r="D14" t="n">
-        <v>0.01034269761294127</v>
+        <v>0.0007641820702701807</v>
       </c>
     </row>
     <row r="15">
@@ -653,13 +653,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.000391108012991026</v>
+        <v>0.04633815959095955</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.006800549570471048</v>
+        <v>-0.00226964894682169</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.002876576269045472</v>
+        <v>0.0007653766078874469</v>
       </c>
     </row>
     <row r="16">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.01620076596736908</v>
+        <v>-0.2160795778036118</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.01673781685531139</v>
+        <v>0.006675384938716888</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.01629587449133396</v>
+        <v>0.03570014983415604</v>
       </c>
     </row>
     <row r="17">
@@ -685,13 +685,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.004542479291558266</v>
+        <v>0.06251940131187439</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.009366821497678757</v>
+        <v>-0.002404148923233151</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.00698915496468544</v>
+        <v>-0.001831016503274441</v>
       </c>
     </row>
     <row r="18">
@@ -701,13 +701,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.006941592320799828</v>
+        <v>0.08510274440050125</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.009687867946922779</v>
+        <v>-0.002899401122704148</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0001751307863742113</v>
+        <v>-0.001309971208684146</v>
       </c>
     </row>
     <row r="19">
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.000571905286051333</v>
+        <v>0.01770724356174469</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.001803097897209227</v>
+        <v>-0.001039577182382345</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0009619542979635298</v>
+        <v>-0.003434424288570881</v>
       </c>
     </row>
     <row r="20">
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.008007976226508617</v>
+        <v>-0.1092842668294907</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.01083102449774742</v>
+        <v>0.004811366088688374</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0001425562222721055</v>
+        <v>-0.01754098758101463</v>
       </c>
     </row>
     <row r="21">
@@ -749,13 +749,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.0004036712925881147</v>
+        <v>-0.04640455543994904</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.006191482301801443</v>
+        <v>0.001807436463423073</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.002523976378142834</v>
+        <v>0.0007095334585756063</v>
       </c>
     </row>
     <row r="22">
@@ -765,13 +765,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.001173584605567157</v>
+        <v>0.105216421186924</v>
       </c>
       <c r="C22" t="n">
-        <v>0.006670415867120028</v>
+        <v>-0.005034010857343674</v>
       </c>
       <c r="D22" t="n">
-        <v>0.002227860735729337</v>
+        <v>-0.003898519091308117</v>
       </c>
     </row>
     <row r="23">
@@ -781,13 +781,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.001110967481508851</v>
+        <v>0.05267399922013283</v>
       </c>
       <c r="C23" t="n">
-        <v>0.009511838667094707</v>
+        <v>-0.00289115053601563</v>
       </c>
       <c r="D23" t="n">
-        <v>0.003210895927622914</v>
+        <v>-0.001245379797182977</v>
       </c>
     </row>
     <row r="24">
@@ -797,13 +797,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.0005954725202172995</v>
+        <v>0.05319169908761978</v>
       </c>
       <c r="C24" t="n">
-        <v>0.003326764795929193</v>
+        <v>-0.00198244652710855</v>
       </c>
       <c r="D24" t="n">
-        <v>0.001815828494727612</v>
+        <v>-0.0005819602520205081</v>
       </c>
     </row>
     <row r="25">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.0001312583481194451</v>
+        <v>0.1325014531612396</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0003422020527068526</v>
+        <v>-0.003212285693734884</v>
       </c>
       <c r="D25" t="n">
-        <v>3.492193718557246e-05</v>
+        <v>-0.07663127779960632</v>
       </c>
     </row>
     <row r="26">
@@ -829,13 +829,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.001524763996712863</v>
+        <v>0.04419700801372528</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.007761962711811066</v>
+        <v>-0.00173686514608562</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.00435408903285861</v>
+        <v>-0.002678859746083617</v>
       </c>
     </row>
     <row r="27">
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.01270182989537716</v>
+        <v>0.1104402467608452</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.01560982968658209</v>
+        <v>-0.00535086402669549</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.01434883195906878</v>
+        <v>-0.002560575725510716</v>
       </c>
     </row>
     <row r="28">
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.001842098776251078</v>
+        <v>0.02584009617567062</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.002099859993904829</v>
+        <v>-0.00129999069031328</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.001865758211351931</v>
+        <v>0.0003856460971292108</v>
       </c>
     </row>
     <row r="29">
@@ -877,13 +877,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.0002904995053540915</v>
+        <v>0.1086677312850952</v>
       </c>
       <c r="C29" t="n">
-        <v>0.006926883943378925</v>
+        <v>-0.005611270200461149</v>
       </c>
       <c r="D29" t="n">
-        <v>0.002924182452261448</v>
+        <v>0.0004924066597595811</v>
       </c>
     </row>
     <row r="30">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.0002350152644794434</v>
+        <v>0.03171630948781967</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.006841296330094337</v>
+        <v>-0.001247346517629921</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.003309273160994053</v>
+        <v>-0.003266423940658569</v>
       </c>
     </row>
     <row r="31">
@@ -909,13 +909,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.001053461572155356</v>
+        <v>-0.1169824302196503</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.001065496588125825</v>
+        <v>0.00579683855175972</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.001071088016033173</v>
+        <v>0.0006824518204666674</v>
       </c>
     </row>
     <row r="32">
@@ -925,13 +925,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.001753551186993718</v>
+        <v>0.008835122920572758</v>
       </c>
       <c r="C32" t="n">
-        <v>0.009156284853816032</v>
+        <v>0.0002039357350440696</v>
       </c>
       <c r="D32" t="n">
-        <v>0.005159280728548765</v>
+        <v>-0.005174773745238781</v>
       </c>
     </row>
     <row r="33">
@@ -941,13 +941,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.006969323847442865</v>
+        <v>-0.1849420219659805</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.006343540269881487</v>
+        <v>0.0083877919241786</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.006959139369428158</v>
+        <v>0.005671401042491198</v>
       </c>
     </row>
     <row r="34">
@@ -957,13 +957,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.01175776869058609</v>
+        <v>0.04160193726420403</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.01212282665073872</v>
+        <v>-0.002133975271135569</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0007993548642843962</v>
+        <v>0.0004115342162549496</v>
       </c>
     </row>
     <row r="35">
@@ -973,13 +973,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.0004104734107386321</v>
+        <v>0.1282298415899277</v>
       </c>
       <c r="C35" t="n">
-        <v>0.001350050210021436</v>
+        <v>-0.006297231651842594</v>
       </c>
       <c r="D35" t="n">
-        <v>0.000795824802480638</v>
+        <v>2.116957330144942e-05</v>
       </c>
     </row>
     <row r="36">
@@ -989,13 +989,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.00293352990411222</v>
+        <v>-0.09727929532527924</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.01228908076882362</v>
+        <v>0.003881561337038875</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.006851606536656618</v>
+        <v>0.02425886504352093</v>
       </c>
     </row>
     <row r="37">
@@ -1005,13 +1005,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.0008884431445039809</v>
+        <v>0.07491426914930344</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.007960491813719273</v>
+        <v>-0.003527592634782195</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.002872409299015999</v>
+        <v>-0.007531611248850822</v>
       </c>
     </row>
     <row r="38">
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.00459614209830761</v>
+        <v>-0.2030527889728546</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.004766777157783508</v>
+        <v>0.003600494936108589</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0003559644392225891</v>
+        <v>0.09587442129850388</v>
       </c>
     </row>
     <row r="39">
@@ -1037,13 +1037,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.002146158134564757</v>
+        <v>-0.2019424289464951</v>
       </c>
       <c r="C39" t="n">
-        <v>0.002486679702997208</v>
+        <v>0.004636838100850582</v>
       </c>
       <c r="D39" t="n">
-        <v>0.00218919781036675</v>
+        <v>0.06737948954105377</v>
       </c>
     </row>
     <row r="40">
@@ -1053,13 +1053,13 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.001064908923581243</v>
+        <v>0.003277248935773969</v>
       </c>
       <c r="C40" t="n">
-        <v>0.001051463535986841</v>
+        <v>-0.0004553320177365094</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0009891758672893047</v>
+        <v>0.001277600065805018</v>
       </c>
     </row>
     <row r="41">
@@ -1069,13 +1069,13 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.005292654037475586</v>
+        <v>0.1488624215126038</v>
       </c>
       <c r="C41" t="n">
-        <v>0.009115384891629219</v>
+        <v>-0.00716354651376605</v>
       </c>
       <c r="D41" t="n">
-        <v>0.007478268817067146</v>
+        <v>0.0007361019961535931</v>
       </c>
     </row>
     <row r="42">
@@ -1085,13 +1085,13 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.008130456320941448</v>
+        <v>-0.04393814876675606</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.01089112740010023</v>
+        <v>0.002473825821653008</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.0001175871511804871</v>
+        <v>0.0003589136467780918</v>
       </c>
     </row>
     <row r="43">
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.0009402111754752696</v>
+        <v>0.1464271545410156</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.008615655824542046</v>
+        <v>-0.006733681075274944</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.003160739783197641</v>
+        <v>0.005103395786136389</v>
       </c>
     </row>
     <row r="44">
@@ -1117,13 +1117,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.0007990297744981945</v>
+        <v>8.127816545311362e-05</v>
       </c>
       <c r="C44" t="n">
-        <v>0.007736825384199619</v>
+        <v>5.238779340288602e-05</v>
       </c>
       <c r="D44" t="n">
-        <v>0.003864755621179938</v>
+        <v>-0.0002768994017969817</v>
       </c>
     </row>
     <row r="45">
@@ -1133,13 +1133,13 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.0006392622017301619</v>
+        <v>0.1565737128257751</v>
       </c>
       <c r="C45" t="n">
-        <v>0.000448773498646915</v>
+        <v>-0.007242321036756039</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0005692265112884343</v>
+        <v>0.004117792006582022</v>
       </c>
     </row>
     <row r="46">
@@ -1149,13 +1149,13 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.001874825567938387</v>
+        <v>-0.002169058192521334</v>
       </c>
       <c r="C46" t="n">
-        <v>0.008865900337696075</v>
+        <v>0.000561063177883625</v>
       </c>
       <c r="D46" t="n">
-        <v>0.002764410572126508</v>
+        <v>-0.0004030347336083651</v>
       </c>
     </row>
     <row r="47">
@@ -1165,13 +1165,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.003729891264811158</v>
+        <v>-0.205956757068634</v>
       </c>
       <c r="C47" t="n">
-        <v>0.00517747551202774</v>
+        <v>0.008528538979589939</v>
       </c>
       <c r="D47" t="n">
-        <v>0.00465370761230588</v>
+        <v>0.0117045184597373</v>
       </c>
     </row>
     <row r="48">
@@ -1181,13 +1181,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.005564862862229347</v>
+        <v>-0.1420414298772812</v>
       </c>
       <c r="C48" t="n">
-        <v>0.007837746292352676</v>
+        <v>0.007142272777855396</v>
       </c>
       <c r="D48" t="n">
-        <v>0.006761273369193077</v>
+        <v>-0.0006962455227039754</v>
       </c>
     </row>
     <row r="49">
@@ -1197,13 +1197,13 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.01500719599425793</v>
+        <v>0.1563747227191925</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0151599170640111</v>
+        <v>-0.004451786633580923</v>
       </c>
       <c r="D49" t="n">
-        <v>0.01476708985865116</v>
+        <v>-0.05262139439582825</v>
       </c>
     </row>
     <row r="50">
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-1.773146323102992e-05</v>
+        <v>0.152051717042923</v>
       </c>
       <c r="C50" t="n">
-        <v>0.007473292760550976</v>
+        <v>-0.007791033480316401</v>
       </c>
       <c r="D50" t="n">
-        <v>0.003382063936442137</v>
+        <v>0.0001624426950002089</v>
       </c>
     </row>
     <row r="51">
@@ -1229,13 +1229,13 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.000689992681145668</v>
+        <v>0.0529634952545166</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.0005124538438394666</v>
+        <v>-0.001173566561192274</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.0006225890247151256</v>
+        <v>-0.002051750663667917</v>
       </c>
     </row>
     <row r="52">
@@ -1245,13 +1245,13 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.0002814772888086736</v>
+        <v>-0.0002165262412745506</v>
       </c>
       <c r="C52" t="n">
-        <v>0.006967881694436073</v>
+        <v>-7.073227607179433e-05</v>
       </c>
       <c r="D52" t="n">
-        <v>0.002943147206678987</v>
+        <v>0.0001912842271849513</v>
       </c>
     </row>
     <row r="53">
@@ -1261,13 +1261,13 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.007862534373998642</v>
+        <v>-0.02006476372480392</v>
       </c>
       <c r="C53" t="n">
-        <v>0.01132296491414309</v>
+        <v>0.001431843498721719</v>
       </c>
       <c r="D53" t="n">
-        <v>0.000980952987447381</v>
+        <v>0.001015824964269996</v>
       </c>
     </row>
     <row r="54">
@@ -1277,13 +1277,13 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.004817670676857233</v>
+        <v>-0.1375460177659988</v>
       </c>
       <c r="C54" t="n">
-        <v>0.005909612402319908</v>
+        <v>0.00671232957392931</v>
       </c>
       <c r="D54" t="n">
-        <v>0.005679202731698751</v>
+        <v>0.001430865610018373</v>
       </c>
     </row>
     <row r="55">
@@ -1293,13 +1293,13 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.0005208844668231905</v>
+        <v>0.1952669769525528</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.003030570223927498</v>
+        <v>-0.006281730253249407</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.001181933446787298</v>
+        <v>0.079503133893013</v>
       </c>
     </row>
     <row r="56">
@@ -1309,13 +1309,13 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.00117984670214355</v>
+        <v>-0.1397220343351364</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.009603166021406651</v>
+        <v>0.006096682976931334</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.003177563892677426</v>
+        <v>-0.01527007855474949</v>
       </c>
     </row>
     <row r="57">
@@ -1325,13 +1325,13 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.001762407831847668</v>
+        <v>-0.05985990539193153</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.002481999574229121</v>
+        <v>0.002905612345784903</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.002122597303241491</v>
+        <v>0.005274107214063406</v>
       </c>
     </row>
     <row r="58">
@@ -1341,13 +1341,13 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.0002224893105449155</v>
+        <v>-0.1796072423458099</v>
       </c>
       <c r="C58" t="n">
-        <v>0.008313549682497978</v>
+        <v>0.008562878705561161</v>
       </c>
       <c r="D58" t="n">
-        <v>0.003827322041615844</v>
+        <v>-0.0007784665212966502</v>
       </c>
     </row>
     <row r="59">
@@ -1357,13 +1357,13 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.008750191889703274</v>
+        <v>-0.08537760376930237</v>
       </c>
       <c r="C59" t="n">
-        <v>0.01336623169481754</v>
+        <v>0.003338197711855173</v>
       </c>
       <c r="D59" t="n">
-        <v>0.001208198489621282</v>
+        <v>0.0006832146318629384</v>
       </c>
     </row>
     <row r="60">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.0008571594953536987</v>
+        <v>-0.1234717592597008</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.007609772495925426</v>
+        <v>0.003823484759777784</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.002852581441402435</v>
+        <v>0.04939286410808563</v>
       </c>
     </row>
     <row r="61">
@@ -1389,13 +1389,13 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.0005422676913440228</v>
+        <v>0.1307285726070404</v>
       </c>
       <c r="C61" t="n">
-        <v>0.003050687024369836</v>
+        <v>-0.005982749629765749</v>
       </c>
       <c r="D61" t="n">
-        <v>0.00150303088594228</v>
+        <v>5.683982453774661e-05</v>
       </c>
     </row>
     <row r="62">
@@ -1405,13 +1405,13 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.0004269300261512399</v>
+        <v>-0.1945208013057709</v>
       </c>
       <c r="C62" t="n">
-        <v>0.008337181061506271</v>
+        <v>0.00441216304898262</v>
       </c>
       <c r="D62" t="n">
-        <v>0.00394662469625473</v>
+        <v>0.07015737891197205</v>
       </c>
     </row>
     <row r="63">
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.003319310722872615</v>
+        <v>-0.1353322714567184</v>
       </c>
       <c r="C63" t="n">
-        <v>0.003787801368162036</v>
+        <v>0.005592446774244308</v>
       </c>
       <c r="D63" t="n">
-        <v>0.003508942434564233</v>
+        <v>-0.03132885694503784</v>
       </c>
     </row>
     <row r="64">
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.00082455447409302</v>
+        <v>-0.0268041156232357</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.006870726123452187</v>
+        <v>0.001074247760698199</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.002619412261992693</v>
+        <v>0.003506309119984508</v>
       </c>
     </row>
     <row r="65">
@@ -1453,13 +1453,13 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.003413602244108915</v>
+        <v>-0.1530031561851501</v>
       </c>
       <c r="C65" t="n">
-        <v>0.003002103418111801</v>
+        <v>0.007834246382117271</v>
       </c>
       <c r="D65" t="n">
-        <v>0.003456456121057272</v>
+        <v>-0.0006813454674556851</v>
       </c>
     </row>
     <row r="66">
@@ -1469,13 +1469,13 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.0006342441774904728</v>
+        <v>-0.05831818282604218</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.008945093490183353</v>
+        <v>0.002705063903704286</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.004264992196112871</v>
+        <v>3.365263546584174e-05</v>
       </c>
     </row>
     <row r="67">
@@ -1485,13 +1485,13 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.002402795013040304</v>
+        <v>0.08065950870513916</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.002772505860775709</v>
+        <v>-0.002991466782987118</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.002708589192479849</v>
+        <v>-0.001482235034927726</v>
       </c>
     </row>
     <row r="68">
@@ -1501,13 +1501,13 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.0009402832365594804</v>
+        <v>-0.0617273673415184</v>
       </c>
       <c r="C68" t="n">
-        <v>0.00914942380040884</v>
+        <v>0.002615602454170585</v>
       </c>
       <c r="D68" t="n">
-        <v>0.00467823538929224</v>
+        <v>0.001895701978355646</v>
       </c>
     </row>
     <row r="69">
@@ -1517,13 +1517,13 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.001446873648092151</v>
+        <v>0.1903062611818314</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.008798612281680107</v>
+        <v>-0.007270670961588621</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.002870827913284302</v>
+        <v>0.0355554036796093</v>
       </c>
     </row>
     <row r="70">
@@ -1533,13 +1533,13 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-5.67843635508325e-05</v>
+        <v>-0.01738774031400681</v>
       </c>
       <c r="C70" t="n">
-        <v>0.006920302752405405</v>
+        <v>-0.0004725884646177292</v>
       </c>
       <c r="D70" t="n">
-        <v>0.003014515619724989</v>
+        <v>0.004916556645184755</v>
       </c>
     </row>
     <row r="71">
@@ -1549,13 +1549,13 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.002360156970098615</v>
+        <v>-0.1323260962963104</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.01025897357612848</v>
+        <v>0.005705974064767361</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.005840775556862354</v>
+        <v>-0.01940066926181316</v>
       </c>
     </row>
     <row r="72">
@@ -1565,13 +1565,13 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.0001546370331197977</v>
+        <v>-0.04764671251177788</v>
       </c>
       <c r="C72" t="n">
-        <v>0.006974188145250082</v>
+        <v>0.00223946082405746</v>
       </c>
       <c r="D72" t="n">
-        <v>0.003101344453170896</v>
+        <v>-0.00073500961298123</v>
       </c>
     </row>
     <row r="73">
@@ -1581,13 +1581,13 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>8.890203025657684e-05</v>
+        <v>0.1983198076486588</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.007148823235183954</v>
+        <v>-0.00976938009262085</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.003098143730312586</v>
+        <v>-0.0005002619582228363</v>
       </c>
     </row>
     <row r="74">
@@ -1597,13 +1597,13 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-0.0004964389372617006</v>
+        <v>0.09412331879138947</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.001560098142363131</v>
+        <v>-0.00357246003113687</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.0009361779666505754</v>
+        <v>-0.0008015659404918551</v>
       </c>
     </row>
     <row r="75">
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-2.996223702211864e-05</v>
+        <v>-0.03310608863830566</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.0006128110107965767</v>
+        <v>0.001412994926795363</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.0002506655000615865</v>
+        <v>-0.0003662446106318384</v>
       </c>
     </row>
     <row r="76">
@@ -1629,13 +1629,13 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-0.002984356367960572</v>
+        <v>-0.1142232045531273</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.009474074468016624</v>
+        <v>0.004210514482110739</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.006096472032368183</v>
+        <v>0.03087472543120384</v>
       </c>
     </row>
     <row r="77">
@@ -1645,13 +1645,13 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.0008020135574042797</v>
+        <v>-0.1779150515794754</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.00627143494784832</v>
+        <v>0.006317939143627882</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.002309130039066076</v>
+        <v>-0.05942441150546074</v>
       </c>
     </row>
     <row r="78">
@@ -1661,13 +1661,13 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1.741775486152619e-05</v>
+        <v>0.07443898171186447</v>
       </c>
       <c r="C78" t="n">
-        <v>0.007122319657355547</v>
+        <v>-0.003797750687226653</v>
       </c>
       <c r="D78" t="n">
-        <v>0.003273399313911796</v>
+        <v>-0.0004979982622899115</v>
       </c>
     </row>
     <row r="79">
@@ -1677,13 +1677,13 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-0.04031210020184517</v>
+        <v>-0.001292737550102174</v>
       </c>
       <c r="C79" t="n">
-        <v>0.07165312767028809</v>
+        <v>0.001366592128761113</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.003836153773590922</v>
+        <v>0.003323401790112257</v>
       </c>
     </row>
     <row r="80">
@@ -1693,13 +1693,13 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-0.0001198311510961503</v>
+        <v>-0.05241765826940536</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.005842681042850018</v>
+        <v>0.002565620699897408</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.002753088250756264</v>
+        <v>0.00503919180482626</v>
       </c>
     </row>
     <row r="81">
@@ -1709,13 +1709,13 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-0.0003261008241679519</v>
+        <v>-0.09375660866498947</v>
       </c>
       <c r="C81" t="n">
-        <v>0.005926723126322031</v>
+        <v>0.003529810812324286</v>
       </c>
       <c r="D81" t="n">
-        <v>0.002470044884830713</v>
+        <v>0.0008021871326491237</v>
       </c>
     </row>
     <row r="82">
@@ -1725,13 +1725,13 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-0.0001984744740184397</v>
+        <v>-0.09451323747634888</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.007177555933594704</v>
+        <v>0.004513368476182222</v>
       </c>
       <c r="D82" t="n">
-        <v>-0.003278949996456504</v>
+        <v>-0.001331250416114926</v>
       </c>
     </row>
     <row r="83">
@@ -1741,13 +1741,13 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>-0.001207701861858368</v>
+        <v>0.06347692012786865</v>
       </c>
       <c r="C83" t="n">
-        <v>0.008561630733311176</v>
+        <v>-0.00314742443151772</v>
       </c>
       <c r="D83" t="n">
-        <v>0.002936235163360834</v>
+        <v>0.0006022244924679399</v>
       </c>
     </row>
     <row r="84">
@@ -1757,13 +1757,13 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.0004630359180737287</v>
+        <v>-0.1856643706560135</v>
       </c>
       <c r="C84" t="n">
-        <v>0.003532761707901955</v>
+        <v>0.006304115522652864</v>
       </c>
       <c r="D84" t="n">
-        <v>0.001962973969057202</v>
+        <v>0.03026186861097813</v>
       </c>
     </row>
     <row r="85">
@@ -1773,13 +1773,13 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.0003953024570364505</v>
+        <v>0.135605126619339</v>
       </c>
       <c r="C85" t="n">
-        <v>0.007478042971342802</v>
+        <v>-0.005522327963262796</v>
       </c>
       <c r="D85" t="n">
-        <v>0.003662275848910213</v>
+        <v>-0.01767859421670437</v>
       </c>
     </row>
     <row r="86">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>-0.002196815796196461</v>
+        <v>0.1891710013151169</v>
       </c>
       <c r="C86" t="n">
-        <v>-0.002097859745845199</v>
+        <v>-0.00729508837684989</v>
       </c>
       <c r="D86" t="n">
-        <v>-0.00217547407373786</v>
+        <v>-0.01845523528754711</v>
       </c>
     </row>
     <row r="87">
@@ -1805,13 +1805,13 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>-0.0007750361692160368</v>
+        <v>-0.08841810375452042</v>
       </c>
       <c r="C87" t="n">
-        <v>-0.0006976304575800896</v>
+        <v>0.004346027504652739</v>
       </c>
       <c r="D87" t="n">
-        <v>-0.0007813252741470933</v>
+        <v>1.763616455718875e-05</v>
       </c>
     </row>
     <row r="88">
@@ -1821,13 +1821,13 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.001299854717217386</v>
+        <v>-0.1564641296863556</v>
       </c>
       <c r="C88" t="n">
-        <v>0.009260796941816807</v>
+        <v>0.007811469025909901</v>
       </c>
       <c r="D88" t="n">
-        <v>0.004950858652591705</v>
+        <v>0.0001783266925485805</v>
       </c>
     </row>
     <row r="89">
@@ -1837,13 +1837,13 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-0.0009675124892964959</v>
+        <v>-0.1585655510425568</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.009166164323687553</v>
+        <v>0.005856867879629135</v>
       </c>
       <c r="D89" t="n">
-        <v>-0.004675285425037146</v>
+        <v>-0.05771534517407417</v>
       </c>
     </row>
     <row r="90">
@@ -1853,13 +1853,13 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>-0.000200200272956863</v>
+        <v>0.1351199448108673</v>
       </c>
       <c r="C90" t="n">
-        <v>0.01085933856666088</v>
+        <v>-0.006137212738394737</v>
       </c>
       <c r="D90" t="n">
-        <v>0.004260723479092121</v>
+        <v>4.33149907621555e-05</v>
       </c>
     </row>
     <row r="91">
@@ -1869,13 +1869,13 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-0.0004530254809651524</v>
+        <v>0.1600507348775864</v>
       </c>
       <c r="C91" t="n">
-        <v>0.00544136855751276</v>
+        <v>-0.008168445900082588</v>
       </c>
       <c r="D91" t="n">
-        <v>0.002206887351348996</v>
+        <v>0.0006440764991566539</v>
       </c>
     </row>
     <row r="92">
@@ -1885,13 +1885,13 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>-0.001114448881708086</v>
+        <v>0.01696192473173141</v>
       </c>
       <c r="C92" t="n">
-        <v>-0.008601321838796139</v>
+        <v>-0.00119915243703872</v>
       </c>
       <c r="D92" t="n">
-        <v>-0.004534079227596521</v>
+        <v>-0.0004821345792151988</v>
       </c>
     </row>
     <row r="93">
@@ -1901,13 +1901,13 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.004838114604353905</v>
+        <v>-0.1875309497117996</v>
       </c>
       <c r="C93" t="n">
-        <v>-0.00989235658198595</v>
+        <v>0.007903494872152805</v>
       </c>
       <c r="D93" t="n">
-        <v>-0.001542403362691402</v>
+        <v>-0.01646593771874905</v>
       </c>
     </row>
     <row r="94">
@@ -1917,13 +1917,13 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.0001470070128561929</v>
+        <v>0.07408689707517624</v>
       </c>
       <c r="C94" t="n">
-        <v>0.007586597464978695</v>
+        <v>-0.003587790997698903</v>
       </c>
       <c r="D94" t="n">
-        <v>0.003466916969045997</v>
+        <v>-0.004309854935854673</v>
       </c>
     </row>
     <row r="95">
@@ -1933,13 +1933,13 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.005230130162090063</v>
+        <v>-0.08925601840019226</v>
       </c>
       <c r="C95" t="n">
-        <v>-0.009872434660792351</v>
+        <v>0.004463526420295238</v>
       </c>
       <c r="D95" t="n">
-        <v>-0.001299526658840477</v>
+        <v>0.0001262777950614691</v>
       </c>
     </row>
     <row r="96">
@@ -1949,13 +1949,13 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.004071174189448357</v>
+        <v>0.06868215650320053</v>
       </c>
       <c r="C96" t="n">
-        <v>-0.005703231319785118</v>
+        <v>-0.003077841596677899</v>
       </c>
       <c r="D96" t="n">
-        <v>-0.0002921152336057276</v>
+        <v>0.0004534469917416573</v>
       </c>
     </row>
     <row r="97">
@@ -1965,13 +1965,13 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>-0.004398604389280081</v>
+        <v>-0.08366403728723526</v>
       </c>
       <c r="C97" t="n">
-        <v>-0.003224593354389071</v>
+        <v>0.004069516900926828</v>
       </c>
       <c r="D97" t="n">
-        <v>-0.004082300700247288</v>
+        <v>-0.0002523033472243696</v>
       </c>
     </row>
     <row r="98">
@@ -1981,13 +1981,13 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>2.154911271645688e-05</v>
+        <v>0.05628402531147003</v>
       </c>
       <c r="C98" t="n">
-        <v>0.008818044327199459</v>
+        <v>-0.001691696466878057</v>
       </c>
       <c r="D98" t="n">
-        <v>0.003854402806609869</v>
+        <v>-0.00206816173158586</v>
       </c>
     </row>
     <row r="99">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>-0.004477367736399174</v>
+        <v>0.1723961532115936</v>
       </c>
       <c r="C99" t="n">
-        <v>-0.009393167681992054</v>
+        <v>-0.007918214425444603</v>
       </c>
       <c r="D99" t="n">
-        <v>-0.007115519139915705</v>
+        <v>0.004597576335072517</v>
       </c>
     </row>
     <row r="100">
@@ -2013,13 +2013,13 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.0006409226334653795</v>
+        <v>0.0682196170091629</v>
       </c>
       <c r="C100" t="n">
-        <v>0.002795665990561247</v>
+        <v>-0.003342751879245043</v>
       </c>
       <c r="D100" t="n">
-        <v>0.001561048440635204</v>
+        <v>0.0008023709524422884</v>
       </c>
     </row>
     <row r="101">
@@ -2029,13 +2029,13 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>-0.003249799599871039</v>
+        <v>-0.0233098566532135</v>
       </c>
       <c r="C101" t="n">
-        <v>0.003973896149545908</v>
+        <v>0.0002408446162007749</v>
       </c>
       <c r="D101" t="n">
-        <v>0.0002979213022626936</v>
+        <v>0.004140614997595549</v>
       </c>
     </row>
     <row r="102">
@@ -2045,13 +2045,13 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>-0.006589005701243877</v>
+        <v>0.03394168987870216</v>
       </c>
       <c r="C102" t="n">
-        <v>0.007267078850418329</v>
+        <v>-0.001618136069737375</v>
       </c>
       <c r="D102" t="n">
-        <v>-0.0002282912901137024</v>
+        <v>-0.003000847063958645</v>
       </c>
     </row>
     <row r="103">
@@ -2061,13 +2061,13 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>-0.003927857615053654</v>
+        <v>0.01144122146070004</v>
       </c>
       <c r="C103" t="n">
-        <v>-0.004549174569547176</v>
+        <v>-0.0006249853176996112</v>
       </c>
       <c r="D103" t="n">
-        <v>-0.004088800400495529</v>
+        <v>-0.00220461655408144</v>
       </c>
     </row>
     <row r="104">
@@ -2077,13 +2077,13 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>-1.239827543031424e-05</v>
+        <v>0.1146451830863953</v>
       </c>
       <c r="C104" t="n">
-        <v>-0.0005823981482535601</v>
+        <v>-0.004942002706229687</v>
       </c>
       <c r="D104" t="n">
-        <v>-0.0002267608651891351</v>
+        <v>-0.01375365070998669</v>
       </c>
     </row>
     <row r="105">
@@ -2093,13 +2093,13 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>-0.0002981969737447798</v>
+        <v>0.1685284674167633</v>
       </c>
       <c r="C105" t="n">
-        <v>9.031112858792767e-05</v>
+        <v>-0.008545216172933578</v>
       </c>
       <c r="D105" t="n">
-        <v>-0.0001638960238778964</v>
+        <v>1.739856088533998e-06</v>
       </c>
     </row>
     <row r="106">
@@ -2109,13 +2109,13 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>-0.0009354252833873034</v>
+        <v>-0.1788621842861176</v>
       </c>
       <c r="C106" t="n">
-        <v>-0.0008787420811131597</v>
+        <v>0.005260657984763384</v>
       </c>
       <c r="D106" t="n">
-        <v>-0.0008613119134679437</v>
+        <v>0.04534027352929115</v>
       </c>
     </row>
     <row r="107">
@@ -2125,13 +2125,13 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>-0.005877119489014149</v>
+        <v>-0.1033114641904831</v>
       </c>
       <c r="C107" t="n">
-        <v>-0.009309188462793827</v>
+        <v>0.004929292015731335</v>
       </c>
       <c r="D107" t="n">
-        <v>-0.007901376113295555</v>
+        <v>0.0002065067528747022</v>
       </c>
     </row>
     <row r="108">
@@ -2141,13 +2141,13 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.006225570105016232</v>
+        <v>-0.1460612863302231</v>
       </c>
       <c r="C108" t="n">
-        <v>0.008509932085871696</v>
+        <v>0.006732416804879904</v>
       </c>
       <c r="D108" t="n">
-        <v>0.007735475897789001</v>
+        <v>-0.00479954807087779</v>
       </c>
     </row>
     <row r="109">
@@ -2157,13 +2157,13 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.004465990699827671</v>
+        <v>0.1038900315761566</v>
       </c>
       <c r="C109" t="n">
-        <v>-0.00585800688713789</v>
+        <v>-0.004864243324846029</v>
       </c>
       <c r="D109" t="n">
-        <v>-0.0001485746470279992</v>
+        <v>0.003456412348896265</v>
       </c>
     </row>
     <row r="110">
@@ -2173,13 +2173,13 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>-0.0008375399047508836</v>
+        <v>0.006807669065892696</v>
       </c>
       <c r="C110" t="n">
-        <v>0.009877705946564674</v>
+        <v>-0.0006164106889627874</v>
       </c>
       <c r="D110" t="n">
-        <v>0.0034858463332057</v>
+        <v>0.0003997423918917775</v>
       </c>
     </row>
     <row r="111">
@@ -2189,13 +2189,13 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.0007054782472550869</v>
+        <v>0.1430884301662445</v>
       </c>
       <c r="C111" t="n">
-        <v>0.002512946026399732</v>
+        <v>-0.005796358454972506</v>
       </c>
       <c r="D111" t="n">
-        <v>0.001473692362196743</v>
+        <v>-8.151258225552738e-05</v>
       </c>
     </row>
     <row r="112">
@@ -2205,13 +2205,13 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.01650537177920341</v>
+        <v>0.1924995332956314</v>
       </c>
       <c r="C112" t="n">
-        <v>0.0179352629929781</v>
+        <v>-0.006554017774760723</v>
       </c>
       <c r="D112" t="n">
-        <v>0.0171993300318718</v>
+        <v>0.06409425288438797</v>
       </c>
     </row>
     <row r="113">
@@ -2221,13 +2221,13 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>-0.0008227915386669338</v>
+        <v>0.06108225882053375</v>
       </c>
       <c r="C113" t="n">
-        <v>0.006862593814730644</v>
+        <v>-0.002632452873513103</v>
       </c>
       <c r="D113" t="n">
-        <v>0.002617312129586935</v>
+        <v>0.00030001241248101</v>
       </c>
     </row>
     <row r="114">
@@ -2237,13 +2237,13 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>-0.002140762517228723</v>
+        <v>0.07721178233623505</v>
       </c>
       <c r="C114" t="n">
-        <v>-0.01172793190926313</v>
+        <v>-0.003454247256740928</v>
       </c>
       <c r="D114" t="n">
-        <v>-0.006271714344620705</v>
+        <v>-0.01338864956051111</v>
       </c>
     </row>
     <row r="115">
@@ -2253,13 +2253,13 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.00123164220713079</v>
+        <v>0.1273318082094193</v>
       </c>
       <c r="C115" t="n">
-        <v>-0.008635357953608036</v>
+        <v>-0.005670035723596811</v>
       </c>
       <c r="D115" t="n">
-        <v>-0.002982920967042446</v>
+        <v>-0.000136202055728063</v>
       </c>
     </row>
     <row r="116">
@@ -2269,13 +2269,13 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>-0.0002648691297508776</v>
+        <v>0.1636356562376022</v>
       </c>
       <c r="C116" t="n">
-        <v>-0.002731540938839316</v>
+        <v>-0.00810631737112999</v>
       </c>
       <c r="D116" t="n">
-        <v>-0.001501269638538361</v>
+        <v>-0.0004064050444867462</v>
       </c>
     </row>
     <row r="117">
@@ -2285,13 +2285,13 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.0005438756197690964</v>
+        <v>0.0677531510591507</v>
       </c>
       <c r="C117" t="n">
-        <v>-0.006368906237185001</v>
+        <v>-0.003472925396636128</v>
       </c>
       <c r="D117" t="n">
-        <v>-0.002542419591918588</v>
+        <v>0.0001640384871279821</v>
       </c>
     </row>
     <row r="118">
@@ -2301,13 +2301,13 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>1.443752080376726e-05</v>
+        <v>-0.15776027739048</v>
       </c>
       <c r="C118" t="n">
-        <v>0.009115854278206825</v>
+        <v>0.007066742051392794</v>
       </c>
       <c r="D118" t="n">
-        <v>0.003958040382713079</v>
+        <v>-0.008599047549068928</v>
       </c>
     </row>
     <row r="119">
@@ -2317,13 +2317,13 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.001073887338861823</v>
+        <v>0.07154087722301483</v>
       </c>
       <c r="C119" t="n">
-        <v>0.001065133488737047</v>
+        <v>-0.003630465362221003</v>
       </c>
       <c r="D119" t="n">
-        <v>0.001003023120574653</v>
+        <v>5.868144216947258e-05</v>
       </c>
     </row>
     <row r="120">
@@ -2333,13 +2333,13 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>-5.293493450153619e-05</v>
+        <v>0.1793908923864365</v>
       </c>
       <c r="C120" t="n">
-        <v>-0.007800895720720291</v>
+        <v>-0.007837384007871151</v>
       </c>
       <c r="D120" t="n">
-        <v>-0.003501563332974911</v>
+        <v>0.01122648641467094</v>
       </c>
     </row>
     <row r="121">
@@ -2349,13 +2349,13 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.002957749646157026</v>
+        <v>0.02002963609993458</v>
       </c>
       <c r="C121" t="n">
-        <v>0.009629165753722191</v>
+        <v>-0.0007840312900952995</v>
       </c>
       <c r="D121" t="n">
-        <v>0.005960125476121902</v>
+        <v>-0.0006327625014819205</v>
       </c>
     </row>
     <row r="122">
@@ -2365,13 +2365,13 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>-0.0005858566728420556</v>
+        <v>0.1288109719753265</v>
       </c>
       <c r="C122" t="n">
-        <v>0.007713853381574154</v>
+        <v>-0.003672546939924359</v>
       </c>
       <c r="D122" t="n">
-        <v>0.003138011787086725</v>
+        <v>-0.05801860988140106</v>
       </c>
     </row>
     <row r="123">
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>-0.0005942792049609125</v>
+        <v>0.135416716337204</v>
       </c>
       <c r="C123" t="n">
-        <v>-0.001863590558059514</v>
+        <v>-0.006037991493940353</v>
       </c>
       <c r="D123" t="n">
-        <v>-0.0009793442441150546</v>
+        <v>0.01096305903047323</v>
       </c>
     </row>
     <row r="124">
@@ -2397,13 +2397,13 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.06684853881597519</v>
+        <v>0.08914389461278915</v>
       </c>
       <c r="C124" t="n">
-        <v>-0.1354794353246689</v>
+        <v>-0.004317993763834238</v>
       </c>
       <c r="D124" t="n">
-        <v>0.03808501735329628</v>
+        <v>-0.003393111284822226</v>
       </c>
     </row>
     <row r="125">
@@ -2413,13 +2413,13 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>-0.0005403556278906763</v>
+        <v>-0.1547800600528717</v>
       </c>
       <c r="C125" t="n">
-        <v>0.006364306900650263</v>
+        <v>0.003232519840821624</v>
       </c>
       <c r="D125" t="n">
-        <v>0.002543403534218669</v>
+        <v>0.08885238319635391</v>
       </c>
     </row>
     <row r="126">
@@ -2429,13 +2429,13 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.001119799097068608</v>
+        <v>0.1948625445365906</v>
       </c>
       <c r="C126" t="n">
-        <v>0.01192429475486279</v>
+        <v>-0.003837627358734608</v>
       </c>
       <c r="D126" t="n">
-        <v>0.005466110538691282</v>
+        <v>-0.08582452684640884</v>
       </c>
     </row>
     <row r="127">
@@ -2445,13 +2445,13 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.0002419039374217391</v>
+        <v>-0.03214960917830467</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.006046537775546312</v>
+        <v>0.001555406372062862</v>
       </c>
       <c r="D127" t="n">
-        <v>-0.002499874215573072</v>
+        <v>7.393633859464899e-05</v>
       </c>
     </row>
     <row r="128">
@@ -2461,13 +2461,13 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.0003261879319325089</v>
+        <v>0.04010551050305367</v>
       </c>
       <c r="C128" t="n">
-        <v>-0.01033090706914663</v>
+        <v>-0.001996810780838132</v>
       </c>
       <c r="D128" t="n">
-        <v>-0.003818346653133631</v>
+        <v>-0.00225070770829916</v>
       </c>
     </row>
     <row r="129">
@@ -2477,13 +2477,13 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>-0.0001743218308547512</v>
+        <v>-0.153128519654274</v>
       </c>
       <c r="C129" t="n">
-        <v>-0.005948803853243589</v>
+        <v>0.007872701622545719</v>
       </c>
       <c r="D129" t="n">
-        <v>-0.002832159865647554</v>
+        <v>-0.0005622365279123187</v>
       </c>
     </row>
   </sheetData>

--- a/frequencies.xlsx
+++ b/frequencies.xlsx
@@ -445,13 +445,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.1840952336788177</v>
+        <v>1.696432860853747e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>0.007535470183938742</v>
+        <v>-0.01030194666236639</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.02231810241937637</v>
+        <v>-0.01100662164390087</v>
       </c>
     </row>
     <row r="3">
@@ -461,13 +461,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.03192802891135216</v>
+        <v>1.28482696482024e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.0001036008034134284</v>
+        <v>-0.01412288378924131</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.003219404956325889</v>
+        <v>-0.004044552333652973</v>
       </c>
     </row>
     <row r="4">
@@ -477,13 +477,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1225029155611992</v>
+        <v>1.90568954394621e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.005605622194707394</v>
+        <v>-0.002855349564924836</v>
       </c>
       <c r="D4" t="n">
-        <v>0.006694207899272442</v>
+        <v>0.0001263399899471551</v>
       </c>
     </row>
     <row r="5">
@@ -493,13 +493,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.146861732006073</v>
+        <v>1.221093839376408e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00365769281052053</v>
+        <v>-0.01301437709480524</v>
       </c>
       <c r="D5" t="n">
-        <v>0.06988939642906189</v>
+        <v>-0.009165088646113873</v>
       </c>
     </row>
     <row r="6">
@@ -509,13 +509,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.0381476990878582</v>
+        <v>1.131864806325211e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0009215770987793803</v>
+        <v>0.03887109830975533</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002930273301899433</v>
+        <v>-0.006259980145841837</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.166102796792984</v>
+        <v>-1.100141489018824e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>0.006128130480647087</v>
+        <v>0.00840394664555788</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.05391233414411545</v>
+        <v>-0.003152512479573488</v>
       </c>
     </row>
     <row r="8">
@@ -541,13 +541,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1595820486545563</v>
+        <v>-4.079511128907143e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.005823531188070774</v>
+        <v>-0.01638245396316051</v>
       </c>
       <c r="D8" t="n">
-        <v>0.06124323979020119</v>
+        <v>-0.00172103475779295</v>
       </c>
     </row>
     <row r="9">
@@ -557,13 +557,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.147405743598938</v>
+        <v>-1.541384335723706e-07</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.002847629599273205</v>
+        <v>-0.05662934109568596</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1003423482179642</v>
+        <v>0.006130948662757874</v>
       </c>
     </row>
     <row r="10">
@@ -573,13 +573,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.08968954533338547</v>
+        <v>-1.659775108464601e-07</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.003184733679518104</v>
+        <v>-0.004918457008898258</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.03963819891214371</v>
+        <v>0.0007221953710541129</v>
       </c>
     </row>
     <row r="11">
@@ -589,13 +589,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.1180892735719681</v>
+        <v>-7.463247442274223e-08</v>
       </c>
       <c r="C11" t="n">
-        <v>0.005898165516555309</v>
+        <v>-0.001852864865213633</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0002628120710141957</v>
+        <v>-0.01129858754575253</v>
       </c>
     </row>
     <row r="12">
@@ -605,13 +605,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.08295014500617981</v>
+        <v>4.471602821354281e-08</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.003907333593815565</v>
+        <v>0.01327323447912931</v>
       </c>
       <c r="D12" t="n">
-        <v>0.002753861248493195</v>
+        <v>0.005255949683487415</v>
       </c>
     </row>
     <row r="13">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1383734345436096</v>
+        <v>7.326679707375661e-08</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.005764704663306475</v>
+        <v>-0.002153990557417274</v>
       </c>
       <c r="D13" t="n">
-        <v>0.02785073406994343</v>
+        <v>-0.005113157443702221</v>
       </c>
     </row>
     <row r="14">
@@ -637,13 +637,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.003365649376064539</v>
+        <v>-1.108410501160506e-07</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0009918769355863333</v>
+        <v>-0.003495641984045506</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0007641820702701807</v>
+        <v>0.009128821082413197</v>
       </c>
     </row>
     <row r="15">
@@ -653,13 +653,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.04633815959095955</v>
+        <v>1.371331421751165e-07</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.00226964894682169</v>
+        <v>-0.008062781766057014</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0007653766078874469</v>
+        <v>-0.008597169071435928</v>
       </c>
     </row>
     <row r="16">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.2160795778036118</v>
+        <v>-1.062805878859763e-07</v>
       </c>
       <c r="C16" t="n">
-        <v>0.006675384938716888</v>
+        <v>0.01649385876953602</v>
       </c>
       <c r="D16" t="n">
-        <v>0.03570014983415604</v>
+        <v>-0.007484924979507923</v>
       </c>
     </row>
     <row r="17">
@@ -685,13 +685,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.06251940131187439</v>
+        <v>1.333337085185349e-08</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.002404148923233151</v>
+        <v>-0.05856583639979362</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.001831016503274441</v>
+        <v>0.0006583139183931053</v>
       </c>
     </row>
     <row r="18">
@@ -701,13 +701,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.08510274440050125</v>
+        <v>3.478235655052231e-08</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.002899401122704148</v>
+        <v>0.008694520220160484</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.001309971208684146</v>
+        <v>-0.001943364390172064</v>
       </c>
     </row>
     <row r="19">
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.01770724356174469</v>
+        <v>3.73239821271909e-08</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.001039577182382345</v>
+        <v>0.01458379998803139</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.003434424288570881</v>
+        <v>5.58573919988703e-05</v>
       </c>
     </row>
     <row r="20">
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.1092842668294907</v>
+        <v>-4.633524497421604e-08</v>
       </c>
       <c r="C20" t="n">
-        <v>0.004811366088688374</v>
+        <v>0.00289706327021122</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.01754098758101463</v>
+        <v>0.005472323391586542</v>
       </c>
     </row>
     <row r="21">
@@ -749,13 +749,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.04640455543994904</v>
+        <v>1.106705411757503e-07</v>
       </c>
       <c r="C21" t="n">
-        <v>0.001807436463423073</v>
+        <v>0.005096709821373224</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0007095334585756063</v>
+        <v>0.003316175192594528</v>
       </c>
     </row>
     <row r="22">
@@ -765,13 +765,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.105216421186924</v>
+        <v>-2.005765367130152e-07</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.005034010857343674</v>
+        <v>-0.02018707245588303</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.003898519091308117</v>
+        <v>0.006441677920520306</v>
       </c>
     </row>
     <row r="23">
@@ -781,13 +781,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.05267399922013283</v>
+        <v>-1.77966711589761e-07</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.00289115053601563</v>
+        <v>-0.01178417075425386</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.001245379797182977</v>
+        <v>0.00522645702585578</v>
       </c>
     </row>
     <row r="24">
@@ -797,13 +797,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.05319169908761978</v>
+        <v>9.868479367014515e-08</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.00198244652710855</v>
+        <v>0.02559558860957623</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0005819602520205081</v>
+        <v>0.007184114772826433</v>
       </c>
     </row>
     <row r="25">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1325014531612396</v>
+        <v>2.150992628457971e-08</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.003212285693734884</v>
+        <v>0.01686146110296249</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.07663127779960632</v>
+        <v>0.00494653033092618</v>
       </c>
     </row>
     <row r="26">
@@ -829,13 +829,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.04419700801372528</v>
+        <v>1.752494966922313e-07</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.00173686514608562</v>
+        <v>-0.02161144465208054</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.002678859746083617</v>
+        <v>0.0005208940128795803</v>
       </c>
     </row>
     <row r="27">
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1104402467608452</v>
+        <v>-1.392284048051806e-07</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.00535086402669549</v>
+        <v>-0.01244802307337523</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.002560575725510716</v>
+        <v>-0.001143218018114567</v>
       </c>
     </row>
     <row r="28">
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.02584009617567062</v>
+        <v>-1.534482692022721e-07</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.00129999069031328</v>
+        <v>0.02156998589634895</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0003856460971292108</v>
+        <v>-0.004483689554035664</v>
       </c>
     </row>
     <row r="29">
@@ -877,13 +877,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1086677312850952</v>
+        <v>-1.338858481858551e-07</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.005611270200461149</v>
+        <v>-0.06211493909358978</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0004924066597595811</v>
+        <v>-0.01203374844044447</v>
       </c>
     </row>
     <row r="30">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.03171630948781967</v>
+        <v>-1.995516356601001e-07</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.001247346517629921</v>
+        <v>0.001458982354961336</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.003266423940658569</v>
+        <v>0.003372824983671308</v>
       </c>
     </row>
     <row r="31">
@@ -909,13 +909,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.1169824302196503</v>
+        <v>-1.936857785267421e-07</v>
       </c>
       <c r="C31" t="n">
-        <v>0.00579683855175972</v>
+        <v>0.002059274818748236</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0006824518204666674</v>
+        <v>-0.001217261073179543</v>
       </c>
     </row>
     <row r="32">
@@ -925,13 +925,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.008835122920572758</v>
+        <v>-1.629118173696043e-07</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0002039357350440696</v>
+        <v>-0.001898842747323215</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.005174773745238781</v>
+        <v>0.006390105467289686</v>
       </c>
     </row>
     <row r="33">
@@ -941,13 +941,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.1849420219659805</v>
+        <v>2.181159430847401e-07</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0083877919241786</v>
+        <v>0.04043585062026978</v>
       </c>
       <c r="D33" t="n">
-        <v>0.005671401042491198</v>
+        <v>-0.006896468810737133</v>
       </c>
     </row>
     <row r="34">
@@ -957,13 +957,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.04160193726420403</v>
+        <v>8.557890396332368e-08</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.002133975271135569</v>
+        <v>0.004301365464925766</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0004115342162549496</v>
+        <v>-0.004026758950203657</v>
       </c>
     </row>
     <row r="35">
@@ -973,13 +973,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.1282298415899277</v>
+        <v>1.547522003875201e-07</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.006297231651842594</v>
+        <v>-0.00124504417181015</v>
       </c>
       <c r="D35" t="n">
-        <v>2.116957330144942e-05</v>
+        <v>0.001236467505805194</v>
       </c>
     </row>
     <row r="36">
@@ -989,13 +989,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.09727929532527924</v>
+        <v>1.35605091600155e-07</v>
       </c>
       <c r="C36" t="n">
-        <v>0.003881561337038875</v>
+        <v>-0.01068750396370888</v>
       </c>
       <c r="D36" t="n">
-        <v>0.02425886504352093</v>
+        <v>0.01107252389192581</v>
       </c>
     </row>
     <row r="37">
@@ -1005,13 +1005,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.07491426914930344</v>
+        <v>-6.660293649929372e-08</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.003527592634782195</v>
+        <v>0.01764084585011005</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.007531611248850822</v>
+        <v>0.001706663751974702</v>
       </c>
     </row>
     <row r="38">
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.2030527889728546</v>
+        <v>2.109056680410504e-07</v>
       </c>
       <c r="C38" t="n">
-        <v>0.003600494936108589</v>
+        <v>0.01540476642549038</v>
       </c>
       <c r="D38" t="n">
-        <v>0.09587442129850388</v>
+        <v>-0.002796417567878962</v>
       </c>
     </row>
     <row r="39">
@@ -1037,13 +1037,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.2019424289464951</v>
+        <v>-1.855362796732152e-07</v>
       </c>
       <c r="C39" t="n">
-        <v>0.004636838100850582</v>
+        <v>0.002903661224991083</v>
       </c>
       <c r="D39" t="n">
-        <v>0.06737948954105377</v>
+        <v>0.009654249995946884</v>
       </c>
     </row>
     <row r="40">
@@ -1053,13 +1053,13 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.003277248935773969</v>
+        <v>-1.263119884242769e-07</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.0004553320177365094</v>
+        <v>-0.01421124581247568</v>
       </c>
       <c r="D40" t="n">
-        <v>0.001277600065805018</v>
+        <v>-0.009066615253686905</v>
       </c>
     </row>
     <row r="41">
@@ -1069,13 +1069,13 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.1488624215126038</v>
+        <v>1.468819021965828e-07</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.00716354651376605</v>
+        <v>0.006255180109292269</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0007361019961535931</v>
+        <v>0.009512901306152344</v>
       </c>
     </row>
     <row r="42">
@@ -1085,13 +1085,13 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.04393814876675606</v>
+        <v>-8.984719102045347e-08</v>
       </c>
       <c r="C42" t="n">
-        <v>0.002473825821653008</v>
+        <v>0.01814412325620651</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0003589136467780918</v>
+        <v>-0.001613236614502966</v>
       </c>
     </row>
     <row r="43">
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.1464271545410156</v>
+        <v>-2.396248248714983e-07</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.006733681075274944</v>
+        <v>-0.03917491808533669</v>
       </c>
       <c r="D43" t="n">
-        <v>0.005103395786136389</v>
+        <v>0.002997979521751404</v>
       </c>
     </row>
     <row r="44">
@@ -1117,13 +1117,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>8.127816545311362e-05</v>
+        <v>-4.455837654404604e-08</v>
       </c>
       <c r="C44" t="n">
-        <v>5.238779340288602e-05</v>
+        <v>-0.00460940133780241</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.0002768994017969817</v>
+        <v>0.002609193092212081</v>
       </c>
     </row>
     <row r="45">
@@ -1133,13 +1133,13 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.1565737128257751</v>
+        <v>-1.410193277706639e-07</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.007242321036756039</v>
+        <v>0.004272988997399807</v>
       </c>
       <c r="D45" t="n">
-        <v>0.004117792006582022</v>
+        <v>-0.000541769084520638</v>
       </c>
     </row>
     <row r="46">
@@ -1149,13 +1149,13 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.002169058192521334</v>
+        <v>4.668315156663994e-08</v>
       </c>
       <c r="C46" t="n">
-        <v>0.000561063177883625</v>
+        <v>0.01044661086052656</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.0004030347336083651</v>
+        <v>0.004801397211849689</v>
       </c>
     </row>
     <row r="47">
@@ -1165,13 +1165,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.205956757068634</v>
+        <v>1.634329009903013e-07</v>
       </c>
       <c r="C47" t="n">
-        <v>0.008528538979589939</v>
+        <v>-0.04937857016921043</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0117045184597373</v>
+        <v>0.004933228250592947</v>
       </c>
     </row>
     <row r="48">
@@ -1181,13 +1181,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.1420414298772812</v>
+        <v>1.281130979080558e-09</v>
       </c>
       <c r="C48" t="n">
-        <v>0.007142272777855396</v>
+        <v>-0.008788182400166988</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.0006962455227039754</v>
+        <v>0.006241241469979286</v>
       </c>
     </row>
     <row r="49">
@@ -1197,13 +1197,13 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.1563747227191925</v>
+        <v>7.102488552845898e-08</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.004451786633580923</v>
+        <v>-0.01391621865332127</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.05262139439582825</v>
+        <v>-0.003485169261693954</v>
       </c>
     </row>
     <row r="50">
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.152051717042923</v>
+        <v>7.011957592339968e-08</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.007791033480316401</v>
+        <v>-0.01375042647123337</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0001624426950002089</v>
+        <v>0.01238903123885393</v>
       </c>
     </row>
     <row r="51">
@@ -1229,13 +1229,13 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.0529634952545166</v>
+        <v>2.033001749168761e-07</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.001173566561192274</v>
+        <v>-0.02208392322063446</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.002051750663667917</v>
+        <v>-0.002557390136644244</v>
       </c>
     </row>
     <row r="52">
@@ -1245,13 +1245,13 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.0002165262412745506</v>
+        <v>-8.922530980726151e-08</v>
       </c>
       <c r="C52" t="n">
-        <v>-7.073227607179433e-05</v>
+        <v>-0.01378573663532734</v>
       </c>
       <c r="D52" t="n">
-        <v>0.0001912842271849513</v>
+        <v>-0.003378423629328609</v>
       </c>
     </row>
     <row r="53">
@@ -1261,13 +1261,13 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.02006476372480392</v>
+        <v>1.505003126567317e-07</v>
       </c>
       <c r="C53" t="n">
-        <v>0.001431843498721719</v>
+        <v>0.02428165450692177</v>
       </c>
       <c r="D53" t="n">
-        <v>0.001015824964269996</v>
+        <v>0.0006569330580532551</v>
       </c>
     </row>
     <row r="54">
@@ -1277,13 +1277,13 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.1375460177659988</v>
+        <v>-1.439926506918709e-07</v>
       </c>
       <c r="C54" t="n">
-        <v>0.00671232957392931</v>
+        <v>0.01340659148991108</v>
       </c>
       <c r="D54" t="n">
-        <v>0.001430865610018373</v>
+        <v>0.0006314895581454039</v>
       </c>
     </row>
     <row r="55">
@@ -1293,13 +1293,13 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.1952669769525528</v>
+        <v>1.392718207426924e-08</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.006281730253249407</v>
+        <v>0.01995690725743771</v>
       </c>
       <c r="D55" t="n">
-        <v>0.079503133893013</v>
+        <v>-0.0017891462193802</v>
       </c>
     </row>
     <row r="56">
@@ -1309,13 +1309,13 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.1397220343351364</v>
+        <v>-1.927399466694624e-07</v>
       </c>
       <c r="C56" t="n">
-        <v>0.006096682976931334</v>
+        <v>0.01502743829041719</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.01527007855474949</v>
+        <v>-0.0008049440220929682</v>
       </c>
     </row>
     <row r="57">
@@ -1325,13 +1325,13 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.05985990539193153</v>
+        <v>9.253925981056454e-08</v>
       </c>
       <c r="C57" t="n">
-        <v>0.002905612345784903</v>
+        <v>0.003534474642947316</v>
       </c>
       <c r="D57" t="n">
-        <v>0.005274107214063406</v>
+        <v>-0.007424852810800076</v>
       </c>
     </row>
     <row r="58">
@@ -1341,13 +1341,13 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.1796072423458099</v>
+        <v>-3.544643689679106e-08</v>
       </c>
       <c r="C58" t="n">
-        <v>0.008562878705561161</v>
+        <v>0.006368580739945173</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.0007784665212966502</v>
+        <v>-0.006295655388385057</v>
       </c>
     </row>
     <row r="59">
@@ -1357,13 +1357,13 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.08537760376930237</v>
+        <v>1.337030113290893e-07</v>
       </c>
       <c r="C59" t="n">
-        <v>0.003338197711855173</v>
+        <v>0.01039855927228928</v>
       </c>
       <c r="D59" t="n">
-        <v>0.0006832146318629384</v>
+        <v>0.004495822358876467</v>
       </c>
     </row>
     <row r="60">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.1234717592597008</v>
+        <v>-1.901436377238497e-07</v>
       </c>
       <c r="C60" t="n">
-        <v>0.003823484759777784</v>
+        <v>-0.010447490029037</v>
       </c>
       <c r="D60" t="n">
-        <v>0.04939286410808563</v>
+        <v>0.001893485430628061</v>
       </c>
     </row>
     <row r="61">
@@ -1389,13 +1389,13 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.1307285726070404</v>
+        <v>-1.987485944709988e-07</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.005982749629765749</v>
+        <v>-0.0001652542850933969</v>
       </c>
       <c r="D61" t="n">
-        <v>5.683982453774661e-05</v>
+        <v>0.0007278412231244147</v>
       </c>
     </row>
     <row r="62">
@@ -1405,13 +1405,13 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.1945208013057709</v>
+        <v>-9.077376006416671e-08</v>
       </c>
       <c r="C62" t="n">
-        <v>0.00441216304898262</v>
+        <v>-0.006002272944897413</v>
       </c>
       <c r="D62" t="n">
-        <v>0.07015737891197205</v>
+        <v>-0.0006244213436730206</v>
       </c>
     </row>
     <row r="63">
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.1353322714567184</v>
+        <v>1.441448294059455e-08</v>
       </c>
       <c r="C63" t="n">
-        <v>0.005592446774244308</v>
+        <v>0.002067094435915351</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.03132885694503784</v>
+        <v>0.00836553331464529</v>
       </c>
     </row>
     <row r="64">
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.0268041156232357</v>
+        <v>5.652946200029874e-08</v>
       </c>
       <c r="C64" t="n">
-        <v>0.001074247760698199</v>
+        <v>-0.04002048820257187</v>
       </c>
       <c r="D64" t="n">
-        <v>0.003506309119984508</v>
+        <v>-0.00277482601813972</v>
       </c>
     </row>
     <row r="65">
@@ -1453,13 +1453,13 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.1530031561851501</v>
+        <v>-4.316048318742105e-08</v>
       </c>
       <c r="C65" t="n">
-        <v>0.007834246382117271</v>
+        <v>-0.0756244882941246</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.0006813454674556851</v>
+        <v>-0.01569378189742565</v>
       </c>
     </row>
     <row r="66">
@@ -1469,13 +1469,13 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.05831818282604218</v>
+        <v>-9.979396509152139e-08</v>
       </c>
       <c r="C66" t="n">
-        <v>0.002705063903704286</v>
+        <v>0.000195463711861521</v>
       </c>
       <c r="D66" t="n">
-        <v>3.365263546584174e-05</v>
+        <v>-0.00123770150821656</v>
       </c>
     </row>
     <row r="67">
@@ -1485,13 +1485,13 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.08065950870513916</v>
+        <v>2.314271618786279e-08</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.002991466782987118</v>
+        <v>0.004059541504830122</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.001482235034927726</v>
+        <v>0.0003538978344295174</v>
       </c>
     </row>
     <row r="68">
@@ -1501,13 +1501,13 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.0617273673415184</v>
+        <v>2.109006658201906e-07</v>
       </c>
       <c r="C68" t="n">
-        <v>0.002615602454170585</v>
+        <v>0.02271624840795994</v>
       </c>
       <c r="D68" t="n">
-        <v>0.001895701978355646</v>
+        <v>0.003548433538526297</v>
       </c>
     </row>
     <row r="69">
@@ -1517,13 +1517,13 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.1903062611818314</v>
+        <v>1.650791574547839e-07</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.007270670961588621</v>
+        <v>0.04933773353695869</v>
       </c>
       <c r="D69" t="n">
-        <v>0.0355554036796093</v>
+        <v>-0.006767132319509983</v>
       </c>
     </row>
     <row r="70">
@@ -1533,13 +1533,13 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.01738774031400681</v>
+        <v>6.869341717674615e-08</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.0004725884646177292</v>
+        <v>0.007113813422620296</v>
       </c>
       <c r="D70" t="n">
-        <v>0.004916556645184755</v>
+        <v>-0.002022505505010486</v>
       </c>
     </row>
     <row r="71">
@@ -1549,13 +1549,13 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.1323260962963104</v>
+        <v>-1.217457565871882e-07</v>
       </c>
       <c r="C71" t="n">
-        <v>0.005705974064767361</v>
+        <v>0.004669127985835075</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.01940066926181316</v>
+        <v>0.0004371335089672357</v>
       </c>
     </row>
     <row r="72">
@@ -1565,13 +1565,13 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.04764671251177788</v>
+        <v>4.572333978103416e-08</v>
       </c>
       <c r="C72" t="n">
-        <v>0.00223946082405746</v>
+        <v>-0.01062243711203337</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.00073500961298123</v>
+        <v>-0.002043633721768856</v>
       </c>
     </row>
     <row r="73">
@@ -1581,13 +1581,13 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.1983198076486588</v>
+        <v>1.966277096698832e-07</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.00976938009262085</v>
+        <v>0.0100335581228137</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.0005002619582228363</v>
+        <v>0.003167415736243129</v>
       </c>
     </row>
     <row r="74">
@@ -1597,13 +1597,13 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.09412331879138947</v>
+        <v>1.615329807691523e-07</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.00357246003113687</v>
+        <v>-0.009465905837714672</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.0008015659404918551</v>
+        <v>-0.0008683899650350213</v>
       </c>
     </row>
     <row r="75">
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-0.03310608863830566</v>
+        <v>-2.825468392586572e-08</v>
       </c>
       <c r="C75" t="n">
-        <v>0.001412994926795363</v>
+        <v>-0.01195088494569063</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.0003662446106318384</v>
+        <v>0.003065471537411213</v>
       </c>
     </row>
     <row r="76">
@@ -1629,13 +1629,13 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-0.1142232045531273</v>
+        <v>9.322257454869032e-08</v>
       </c>
       <c r="C76" t="n">
-        <v>0.004210514482110739</v>
+        <v>-6.02909603912849e-05</v>
       </c>
       <c r="D76" t="n">
-        <v>0.03087472543120384</v>
+        <v>-0.003144207410514355</v>
       </c>
     </row>
     <row r="77">
@@ -1645,13 +1645,13 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-0.1779150515794754</v>
+        <v>1.053609395285093e-07</v>
       </c>
       <c r="C77" t="n">
-        <v>0.006317939143627882</v>
+        <v>-0.01765542477369308</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.05942441150546074</v>
+        <v>-0.01450495515018702</v>
       </c>
     </row>
     <row r="78">
@@ -1661,13 +1661,13 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.07443898171186447</v>
+        <v>3.092891986966606e-08</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.003797750687226653</v>
+        <v>0.035113874822855</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.0004979982622899115</v>
+        <v>0.0008516069501638412</v>
       </c>
     </row>
     <row r="79">
@@ -1677,13 +1677,13 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-0.001292737550102174</v>
+        <v>-5.95270073233678e-08</v>
       </c>
       <c r="C79" t="n">
-        <v>0.001366592128761113</v>
+        <v>0.007662021555006504</v>
       </c>
       <c r="D79" t="n">
-        <v>0.003323401790112257</v>
+        <v>0.002228491473942995</v>
       </c>
     </row>
     <row r="80">
@@ -1693,13 +1693,13 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-0.05241765826940536</v>
+        <v>1.162605371973768e-07</v>
       </c>
       <c r="C80" t="n">
-        <v>0.002565620699897408</v>
+        <v>-0.02134506031870842</v>
       </c>
       <c r="D80" t="n">
-        <v>0.00503919180482626</v>
+        <v>0.003672032849863172</v>
       </c>
     </row>
     <row r="81">
@@ -1709,13 +1709,13 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-0.09375660866498947</v>
+        <v>-9.070475215366969e-08</v>
       </c>
       <c r="C81" t="n">
-        <v>0.003529810812324286</v>
+        <v>-0.05015908181667328</v>
       </c>
       <c r="D81" t="n">
-        <v>0.0008021871326491237</v>
+        <v>0.0079276068136096</v>
       </c>
     </row>
     <row r="82">
@@ -1725,13 +1725,13 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-0.09451323747634888</v>
+        <v>1.24897425735071e-07</v>
       </c>
       <c r="C82" t="n">
-        <v>0.004513368476182222</v>
+        <v>-0.003312842221930623</v>
       </c>
       <c r="D82" t="n">
-        <v>-0.001331250416114926</v>
+        <v>-0.005798499565571547</v>
       </c>
     </row>
     <row r="83">
@@ -1741,13 +1741,13 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.06347692012786865</v>
+        <v>-1.949835706227532e-07</v>
       </c>
       <c r="C83" t="n">
-        <v>-0.00314742443151772</v>
+        <v>0.01999615132808685</v>
       </c>
       <c r="D83" t="n">
-        <v>0.0006022244924679399</v>
+        <v>-0.005168579518795013</v>
       </c>
     </row>
     <row r="84">
@@ -1757,13 +1757,13 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>-0.1856643706560135</v>
+        <v>1.636658595316476e-07</v>
       </c>
       <c r="C84" t="n">
-        <v>0.006304115522652864</v>
+        <v>0.01726222969591618</v>
       </c>
       <c r="D84" t="n">
-        <v>0.03026186861097813</v>
+        <v>-0.003132138634100556</v>
       </c>
     </row>
     <row r="85">
@@ -1773,13 +1773,13 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.135605126619339</v>
+        <v>-9.561904334987048e-08</v>
       </c>
       <c r="C85" t="n">
-        <v>-0.005522327963262796</v>
+        <v>-0.03410091623663902</v>
       </c>
       <c r="D85" t="n">
-        <v>-0.01767859421670437</v>
+        <v>0.00651585403829813</v>
       </c>
     </row>
     <row r="86">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.1891710013151169</v>
+        <v>1.520733547977215e-07</v>
       </c>
       <c r="C86" t="n">
-        <v>-0.00729508837684989</v>
+        <v>0.03740640729665756</v>
       </c>
       <c r="D86" t="n">
-        <v>-0.01845523528754711</v>
+        <v>0.0009002387523651123</v>
       </c>
     </row>
     <row r="87">
@@ -1805,13 +1805,13 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>-0.08841810375452042</v>
+        <v>-9.348685159338288e-10</v>
       </c>
       <c r="C87" t="n">
-        <v>0.004346027504652739</v>
+        <v>-0.03147876262664795</v>
       </c>
       <c r="D87" t="n">
-        <v>1.763616455718875e-05</v>
+        <v>0.01566650345921516</v>
       </c>
     </row>
     <row r="88">
@@ -1821,13 +1821,13 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>-0.1564641296863556</v>
+        <v>-7.75015820408953e-08</v>
       </c>
       <c r="C88" t="n">
-        <v>0.007811469025909901</v>
+        <v>-0.006432149559259415</v>
       </c>
       <c r="D88" t="n">
-        <v>0.0001783266925485805</v>
+        <v>-0.003688508877530694</v>
       </c>
     </row>
     <row r="89">
@@ -1837,13 +1837,13 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-0.1585655510425568</v>
+        <v>-1.637367290641123e-07</v>
       </c>
       <c r="C89" t="n">
-        <v>0.005856867879629135</v>
+        <v>-0.01256397645920515</v>
       </c>
       <c r="D89" t="n">
-        <v>-0.05771534517407417</v>
+        <v>0.0042556282132864</v>
       </c>
     </row>
     <row r="90">
@@ -1853,13 +1853,13 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.1351199448108673</v>
+        <v>-1.339757744744929e-07</v>
       </c>
       <c r="C90" t="n">
-        <v>-0.006137212738394737</v>
+        <v>-0.02469287440180779</v>
       </c>
       <c r="D90" t="n">
-        <v>4.33149907621555e-05</v>
+        <v>0.008099698461592197</v>
       </c>
     </row>
     <row r="91">
@@ -1869,13 +1869,13 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.1600507348775864</v>
+        <v>-1.758142218477587e-07</v>
       </c>
       <c r="C91" t="n">
-        <v>-0.008168445900082588</v>
+        <v>-0.005640024784952402</v>
       </c>
       <c r="D91" t="n">
-        <v>0.0006440764991566539</v>
+        <v>-0.007171135395765305</v>
       </c>
     </row>
     <row r="92">
@@ -1885,13 +1885,13 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.01696192473173141</v>
+        <v>1.691887234755995e-07</v>
       </c>
       <c r="C92" t="n">
-        <v>-0.00119915243703872</v>
+        <v>0.01023782324045897</v>
       </c>
       <c r="D92" t="n">
-        <v>-0.0004821345792151988</v>
+        <v>0.003501836443319917</v>
       </c>
     </row>
     <row r="93">
@@ -1901,13 +1901,13 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>-0.1875309497117996</v>
+        <v>1.074342321771837e-07</v>
       </c>
       <c r="C93" t="n">
-        <v>0.007903494872152805</v>
+        <v>0.001076032407581806</v>
       </c>
       <c r="D93" t="n">
-        <v>-0.01646593771874905</v>
+        <v>0.005362042691558599</v>
       </c>
     </row>
     <row r="94">
@@ -1917,13 +1917,13 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.07408689707517624</v>
+        <v>1.889223000262064e-08</v>
       </c>
       <c r="C94" t="n">
-        <v>-0.003587790997698903</v>
+        <v>0.005661914590746164</v>
       </c>
       <c r="D94" t="n">
-        <v>-0.004309854935854673</v>
+        <v>-0.003135363105684519</v>
       </c>
     </row>
     <row r="95">
@@ -1933,13 +1933,13 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-0.08925601840019226</v>
+        <v>2.695635359373227e-08</v>
       </c>
       <c r="C95" t="n">
-        <v>0.004463526420295238</v>
+        <v>0.01572876051068306</v>
       </c>
       <c r="D95" t="n">
-        <v>0.0001262777950614691</v>
+        <v>-0.01087340246886015</v>
       </c>
     </row>
     <row r="96">
@@ -1949,13 +1949,13 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.06868215650320053</v>
+        <v>-1.729243592762941e-07</v>
       </c>
       <c r="C96" t="n">
-        <v>-0.003077841596677899</v>
+        <v>0.002620386891067028</v>
       </c>
       <c r="D96" t="n">
-        <v>0.0004534469917416573</v>
+        <v>-0.002563911722972989</v>
       </c>
     </row>
     <row r="97">
@@ -1965,13 +1965,13 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>-0.08366403728723526</v>
+        <v>2.840842761031581e-08</v>
       </c>
       <c r="C97" t="n">
-        <v>0.004069516900926828</v>
+        <v>-0.01198215503245592</v>
       </c>
       <c r="D97" t="n">
-        <v>-0.0002523033472243696</v>
+        <v>-0.003059760201722383</v>
       </c>
     </row>
     <row r="98">
@@ -1981,13 +1981,13 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.05628402531147003</v>
+        <v>6.998417489967323e-08</v>
       </c>
       <c r="C98" t="n">
-        <v>-0.001691696466878057</v>
+        <v>-0.03021272830665112</v>
       </c>
       <c r="D98" t="n">
-        <v>-0.00206816173158586</v>
+        <v>0.001460790052078664</v>
       </c>
     </row>
     <row r="99">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.1723961532115936</v>
+        <v>8.468130374694738e-08</v>
       </c>
       <c r="C99" t="n">
-        <v>-0.007918214425444603</v>
+        <v>0.03979146480560303</v>
       </c>
       <c r="D99" t="n">
-        <v>0.004597576335072517</v>
+        <v>-0.005138426553457975</v>
       </c>
     </row>
     <row r="100">
@@ -2013,13 +2013,13 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.0682196170091629</v>
+        <v>-1.914662419721935e-07</v>
       </c>
       <c r="C100" t="n">
-        <v>-0.003342751879245043</v>
+        <v>-9.55216892180033e-05</v>
       </c>
       <c r="D100" t="n">
-        <v>0.0008023709524422884</v>
+        <v>-0.001657661166973412</v>
       </c>
     </row>
     <row r="101">
@@ -2029,13 +2029,13 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>-0.0233098566532135</v>
+        <v>-1.242382836608158e-07</v>
       </c>
       <c r="C101" t="n">
-        <v>0.0002408446162007749</v>
+        <v>-0.008564585819840431</v>
       </c>
       <c r="D101" t="n">
-        <v>0.004140614997595549</v>
+        <v>0.001769330468960106</v>
       </c>
     </row>
     <row r="102">
@@ -2045,13 +2045,13 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.03394168987870216</v>
+        <v>1.118315395842728e-07</v>
       </c>
       <c r="C102" t="n">
-        <v>-0.001618136069737375</v>
+        <v>-0.011629993095994</v>
       </c>
       <c r="D102" t="n">
-        <v>-0.003000847063958645</v>
+        <v>-0.00238357437774539</v>
       </c>
     </row>
     <row r="103">
@@ -2061,13 +2061,13 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.01144122146070004</v>
+        <v>1.07576504149165e-07</v>
       </c>
       <c r="C103" t="n">
-        <v>-0.0006249853176996112</v>
+        <v>0.02830968983471394</v>
       </c>
       <c r="D103" t="n">
-        <v>-0.00220461655408144</v>
+        <v>-0.01171484030783176</v>
       </c>
     </row>
     <row r="104">
@@ -2077,13 +2077,13 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.1146451830863953</v>
+        <v>-5.616570319944003e-08</v>
       </c>
       <c r="C104" t="n">
-        <v>-0.004942002706229687</v>
+        <v>-0.001993932528421283</v>
       </c>
       <c r="D104" t="n">
-        <v>-0.01375365070998669</v>
+        <v>0.0064092050306499</v>
       </c>
     </row>
     <row r="105">
@@ -2093,13 +2093,13 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.1685284674167633</v>
+        <v>8.969873022124375e-08</v>
       </c>
       <c r="C105" t="n">
-        <v>-0.008545216172933578</v>
+        <v>0.03262845799326897</v>
       </c>
       <c r="D105" t="n">
-        <v>1.739856088533998e-06</v>
+        <v>0.01429613865911961</v>
       </c>
     </row>
     <row r="106">
@@ -2109,13 +2109,13 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>-0.1788621842861176</v>
+        <v>-8.467265999456686e-09</v>
       </c>
       <c r="C106" t="n">
-        <v>0.005260657984763384</v>
+        <v>-0.02480077929794788</v>
       </c>
       <c r="D106" t="n">
-        <v>0.04534027352929115</v>
+        <v>-0.001488079084083438</v>
       </c>
     </row>
     <row r="107">
@@ -2125,13 +2125,13 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>-0.1033114641904831</v>
+        <v>-6.801658969379787e-08</v>
       </c>
       <c r="C107" t="n">
-        <v>0.004929292015731335</v>
+        <v>0.003736539976671338</v>
       </c>
       <c r="D107" t="n">
-        <v>0.0002065067528747022</v>
+        <v>-0.008111990988254547</v>
       </c>
     </row>
     <row r="108">
@@ -2141,13 +2141,13 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>-0.1460612863302231</v>
+        <v>-1.05496880564715e-07</v>
       </c>
       <c r="C108" t="n">
-        <v>0.006732416804879904</v>
+        <v>0.01683791726827621</v>
       </c>
       <c r="D108" t="n">
-        <v>-0.00479954807087779</v>
+        <v>0.00247075455263257</v>
       </c>
     </row>
     <row r="109">
@@ -2157,13 +2157,13 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.1038900315761566</v>
+        <v>7.932722922987523e-08</v>
       </c>
       <c r="C109" t="n">
-        <v>-0.004864243324846029</v>
+        <v>-0.007422009948641062</v>
       </c>
       <c r="D109" t="n">
-        <v>0.003456412348896265</v>
+        <v>0.002910285256803036</v>
       </c>
     </row>
     <row r="110">
@@ -2173,13 +2173,13 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.006807669065892696</v>
+        <v>-1.974041481389577e-07</v>
       </c>
       <c r="C110" t="n">
-        <v>-0.0006164106889627874</v>
+        <v>0.01540351659059525</v>
       </c>
       <c r="D110" t="n">
-        <v>0.0003997423918917775</v>
+        <v>-0.005625086836516857</v>
       </c>
     </row>
     <row r="111">
@@ -2189,13 +2189,13 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.1430884301662445</v>
+        <v>1.654928780681075e-07</v>
       </c>
       <c r="C111" t="n">
-        <v>-0.005796358454972506</v>
+        <v>-0.005561497993767262</v>
       </c>
       <c r="D111" t="n">
-        <v>-8.151258225552738e-05</v>
+        <v>0.001732931821607053</v>
       </c>
     </row>
     <row r="112">
@@ -2205,13 +2205,13 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.1924995332956314</v>
+        <v>-1.872949155767856e-07</v>
       </c>
       <c r="C112" t="n">
-        <v>-0.006554017774760723</v>
+        <v>0.009168339893221855</v>
       </c>
       <c r="D112" t="n">
-        <v>0.06409425288438797</v>
+        <v>0.005246401764452457</v>
       </c>
     </row>
     <row r="113">
@@ -2221,13 +2221,13 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.06108225882053375</v>
+        <v>-1.513779857020836e-08</v>
       </c>
       <c r="C113" t="n">
-        <v>-0.002632452873513103</v>
+        <v>-0.02053848095238209</v>
       </c>
       <c r="D113" t="n">
-        <v>0.00030001241248101</v>
+        <v>-0.0007827212102711201</v>
       </c>
     </row>
     <row r="114">
@@ -2237,13 +2237,13 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.07721178233623505</v>
+        <v>7.224430476071575e-08</v>
       </c>
       <c r="C114" t="n">
-        <v>-0.003454247256740928</v>
+        <v>-0.0006813177024014294</v>
       </c>
       <c r="D114" t="n">
-        <v>-0.01338864956051111</v>
+        <v>0.005345194134861231</v>
       </c>
     </row>
     <row r="115">
@@ -2253,13 +2253,13 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.1273318082094193</v>
+        <v>-1.178842552462811e-07</v>
       </c>
       <c r="C115" t="n">
-        <v>-0.005670035723596811</v>
+        <v>0.01580410823225975</v>
       </c>
       <c r="D115" t="n">
-        <v>-0.000136202055728063</v>
+        <v>0.005624927580356598</v>
       </c>
     </row>
     <row r="116">
@@ -2269,13 +2269,13 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.1636356562376022</v>
+        <v>-4.544193643596373e-08</v>
       </c>
       <c r="C116" t="n">
-        <v>-0.00810631737112999</v>
+        <v>-3.252753231208771e-06</v>
       </c>
       <c r="D116" t="n">
-        <v>-0.0004064050444867462</v>
+        <v>0.003497890895232558</v>
       </c>
     </row>
     <row r="117">
@@ -2285,13 +2285,13 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.0677531510591507</v>
+        <v>-2.597534098924825e-08</v>
       </c>
       <c r="C117" t="n">
-        <v>-0.003472925396636128</v>
+        <v>-0.0333281047642231</v>
       </c>
       <c r="D117" t="n">
-        <v>0.0001640384871279821</v>
+        <v>0.002819236600771546</v>
       </c>
     </row>
     <row r="118">
@@ -2301,13 +2301,13 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>-0.15776027739048</v>
+        <v>-1.593001286437357e-07</v>
       </c>
       <c r="C118" t="n">
-        <v>0.007066742051392794</v>
+        <v>-0.01045131031423807</v>
       </c>
       <c r="D118" t="n">
-        <v>-0.008599047549068928</v>
+        <v>-0.006080557126551867</v>
       </c>
     </row>
     <row r="119">
@@ -2317,13 +2317,13 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.07154087722301483</v>
+        <v>-2.127919742633821e-07</v>
       </c>
       <c r="C119" t="n">
-        <v>-0.003630465362221003</v>
+        <v>-0.01087351609021425</v>
       </c>
       <c r="D119" t="n">
-        <v>5.868144216947258e-05</v>
+        <v>-0.005994852632284164</v>
       </c>
     </row>
     <row r="120">
@@ -2333,13 +2333,13 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.1793908923864365</v>
+        <v>1.287857998022446e-07</v>
       </c>
       <c r="C120" t="n">
-        <v>-0.007837384007871151</v>
+        <v>0.007358478382229805</v>
       </c>
       <c r="D120" t="n">
-        <v>0.01122648641467094</v>
+        <v>0.007999125868082047</v>
       </c>
     </row>
     <row r="121">
@@ -2349,13 +2349,13 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.02002963609993458</v>
+        <v>-1.20018786020637e-08</v>
       </c>
       <c r="C121" t="n">
-        <v>-0.0007840312900952995</v>
+        <v>-0.009972228668630123</v>
       </c>
       <c r="D121" t="n">
-        <v>-0.0006327625014819205</v>
+        <v>0.001316368114203215</v>
       </c>
     </row>
     <row r="122">
@@ -2365,13 +2365,13 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.1288109719753265</v>
+        <v>-1.525937420865375e-07</v>
       </c>
       <c r="C122" t="n">
-        <v>-0.003672546939924359</v>
+        <v>0.01521044131368399</v>
       </c>
       <c r="D122" t="n">
-        <v>-0.05801860988140106</v>
+        <v>0.0008086301968432963</v>
       </c>
     </row>
     <row r="123">
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.135416716337204</v>
+        <v>-5.885436138441946e-08</v>
       </c>
       <c r="C123" t="n">
-        <v>-0.006037991493940353</v>
+        <v>-0.004780187271535397</v>
       </c>
       <c r="D123" t="n">
-        <v>0.01096305903047323</v>
+        <v>-0.001263945829123259</v>
       </c>
     </row>
     <row r="124">
@@ -2397,13 +2397,13 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.08914389461278915</v>
+        <v>6.859191614694282e-08</v>
       </c>
       <c r="C124" t="n">
-        <v>-0.004317993763834238</v>
+        <v>0.01991062052547932</v>
       </c>
       <c r="D124" t="n">
-        <v>-0.003393111284822226</v>
+        <v>0.001063250005245209</v>
       </c>
     </row>
     <row r="125">
@@ -2413,13 +2413,13 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>-0.1547800600528717</v>
+        <v>-4.233595873870399e-08</v>
       </c>
       <c r="C125" t="n">
-        <v>0.003232519840821624</v>
+        <v>0.03500344231724739</v>
       </c>
       <c r="D125" t="n">
-        <v>0.08885238319635391</v>
+        <v>-0.006084267515689135</v>
       </c>
     </row>
     <row r="126">
@@ -2429,13 +2429,13 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.1948625445365906</v>
+        <v>-6.661637286242694e-08</v>
       </c>
       <c r="C126" t="n">
-        <v>-0.003837627358734608</v>
+        <v>0.01212123595178127</v>
       </c>
       <c r="D126" t="n">
-        <v>-0.08582452684640884</v>
+        <v>-0.005808934569358826</v>
       </c>
     </row>
     <row r="127">
@@ -2445,13 +2445,13 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>-0.03214960917830467</v>
+        <v>6.859515622181789e-08</v>
       </c>
       <c r="C127" t="n">
-        <v>0.001555406372062862</v>
+        <v>0.05611544102430344</v>
       </c>
       <c r="D127" t="n">
-        <v>7.393633859464899e-05</v>
+        <v>0.008169614709913731</v>
       </c>
     </row>
     <row r="128">
@@ -2461,13 +2461,13 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.04010551050305367</v>
+        <v>-1.366095716548443e-07</v>
       </c>
       <c r="C128" t="n">
-        <v>-0.001996810780838132</v>
+        <v>0.01493884157389402</v>
       </c>
       <c r="D128" t="n">
-        <v>-0.00225070770829916</v>
+        <v>-0.002121416386216879</v>
       </c>
     </row>
     <row r="129">
@@ -2477,13 +2477,13 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>-0.153128519654274</v>
+        <v>2.25921397145612e-08</v>
       </c>
       <c r="C129" t="n">
-        <v>0.007872701622545719</v>
+        <v>0.005027350503951311</v>
       </c>
       <c r="D129" t="n">
-        <v>-0.0005622365279123187</v>
+        <v>-0.001026084646582603</v>
       </c>
     </row>
   </sheetData>

--- a/frequencies.xlsx
+++ b/frequencies.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D129"/>
+  <dimension ref="A1:D257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,2049 +441,4097 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Neuron_0</t>
+          <t>Frequency_0</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.696432860853747e-07</v>
+        <v>0.1620902419090271</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.01030194666236639</v>
+        <v>0.1506850123405457</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.01100662164390087</v>
+        <v>-0.01233619078993797</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Neuron_1</t>
+          <t>Frequency_1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.28482696482024e-07</v>
+        <v>-0.08779820054769516</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.01412288378924131</v>
+        <v>-0.0451049692928791</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.004044552333652973</v>
+        <v>-0.004214659798890352</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Neuron_2</t>
+          <t>Frequency_2</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.90568954394621e-07</v>
+        <v>0.1391994953155518</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.002855349564924836</v>
+        <v>-0.002939279191195965</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0001263399899471551</v>
+        <v>0.01315228268504143</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Neuron_3</t>
+          <t>Frequency_3</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.221093839376408e-07</v>
+        <v>0.1727721691131592</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.01301437709480524</v>
+        <v>0.08900514990091324</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.009165088646113873</v>
+        <v>-0.003791916882619262</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Neuron_4</t>
+          <t>Frequency_4</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.131864806325211e-07</v>
+        <v>-0.003775566350668669</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03887109830975533</v>
+        <v>-0.06618022173643112</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.006259980145841837</v>
+        <v>-0.001749445218592882</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Neuron_5</t>
+          <t>Frequency_5</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-1.100141489018824e-08</v>
+        <v>-0.007635404821485281</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00840394664555788</v>
+        <v>-0.01456721965223551</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.003152512479573488</v>
+        <v>0.001594981178641319</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Neuron_6</t>
+          <t>Frequency_6</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-4.079511128907143e-08</v>
+        <v>0.002608941635116935</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.01638245396316051</v>
+        <v>0.1030494645237923</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.00172103475779295</v>
+        <v>-0.001335227978415787</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Neuron_7</t>
+          <t>Frequency_7</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-1.541384335723706e-07</v>
+        <v>0.08476196229457855</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.05662934109568596</v>
+        <v>0.1000616773962975</v>
       </c>
       <c r="D9" t="n">
-        <v>0.006130948662757874</v>
+        <v>-0.0003800195117946714</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Neuron_8</t>
+          <t>Frequency_8</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-1.659775108464601e-07</v>
+        <v>0.02790924906730652</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.004918457008898258</v>
+        <v>-0.03350158408284187</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0007221953710541129</v>
+        <v>-0.00928967259824276</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Neuron_9</t>
+          <t>Frequency_9</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-7.463247442274223e-08</v>
+        <v>-0.08622410148382187</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.001852864865213633</v>
+        <v>0.002249027136713266</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.01129858754575253</v>
+        <v>0.008566510863602161</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Neuron_10</t>
+          <t>Frequency_10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.471602821354281e-08</v>
+        <v>-0.1636539101600647</v>
       </c>
       <c r="C12" t="n">
-        <v>0.01327323447912931</v>
+        <v>-0.0650944858789444</v>
       </c>
       <c r="D12" t="n">
-        <v>0.005255949683487415</v>
+        <v>-0.001524709048680961</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Neuron_11</t>
+          <t>Frequency_11</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7.326679707375661e-08</v>
+        <v>0.1138248443603516</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.002153990557417274</v>
+        <v>0.07387920469045639</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.005113157443702221</v>
+        <v>-0.01082069706171751</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Neuron_12</t>
+          <t>Frequency_12</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-1.108410501160506e-07</v>
+        <v>0.1131850183010101</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.003495641984045506</v>
+        <v>0.0324636735022068</v>
       </c>
       <c r="D14" t="n">
-        <v>0.009128821082413197</v>
+        <v>-0.006291473284363747</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Neuron_13</t>
+          <t>Frequency_13</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.371331421751165e-07</v>
+        <v>-0.1784435957670212</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.008062781766057014</v>
+        <v>-0.100105807185173</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.008597169071435928</v>
+        <v>-0.008913342840969563</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Neuron_14</t>
+          <t>Frequency_14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-1.062805878859763e-07</v>
+        <v>-0.1313813477754593</v>
       </c>
       <c r="C16" t="n">
-        <v>0.01649385876953602</v>
+        <v>-0.07339867204427719</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.007484924979507923</v>
+        <v>0.007127451710402966</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Neuron_15</t>
+          <t>Frequency_15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.333337085185349e-08</v>
+        <v>-0.1023559495806694</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.05856583639979362</v>
+        <v>-0.1142168641090393</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0006583139183931053</v>
+        <v>0.005297670606523752</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Neuron_16</t>
+          <t>Frequency_16</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.478235655052231e-08</v>
+        <v>-0.09460896253585815</v>
       </c>
       <c r="C18" t="n">
-        <v>0.008694520220160484</v>
+        <v>0.03268744051456451</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.001943364390172064</v>
+        <v>-0.00356148649007082</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Neuron_17</t>
+          <t>Frequency_17</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.73239821271909e-08</v>
+        <v>-0.1139103844761848</v>
       </c>
       <c r="C19" t="n">
-        <v>0.01458379998803139</v>
+        <v>-0.06695157289505005</v>
       </c>
       <c r="D19" t="n">
-        <v>5.58573919988703e-05</v>
+        <v>0.005844320170581341</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Neuron_18</t>
+          <t>Frequency_18</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-4.633524497421604e-08</v>
+        <v>0.1067096143960953</v>
       </c>
       <c r="C20" t="n">
-        <v>0.00289706327021122</v>
+        <v>-0.01348884403705597</v>
       </c>
       <c r="D20" t="n">
-        <v>0.005472323391586542</v>
+        <v>-0.01365036051720381</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Neuron_19</t>
+          <t>Frequency_19</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.106705411757503e-07</v>
+        <v>0.0005771052092313766</v>
       </c>
       <c r="C21" t="n">
-        <v>0.005096709821373224</v>
+        <v>-0.1071110218763351</v>
       </c>
       <c r="D21" t="n">
-        <v>0.003316175192594528</v>
+        <v>-0.00902705080807209</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Neuron_20</t>
+          <t>Frequency_20</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-2.005765367130152e-07</v>
+        <v>0.2230391055345535</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.02018707245588303</v>
+        <v>0.1164380833506584</v>
       </c>
       <c r="D22" t="n">
-        <v>0.006441677920520306</v>
+        <v>0.0006571391713805497</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Neuron_21</t>
+          <t>Frequency_21</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-1.77966711589761e-07</v>
+        <v>0.02947002276778221</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.01178417075425386</v>
+        <v>-0.06788411736488342</v>
       </c>
       <c r="D23" t="n">
-        <v>0.00522645702585578</v>
+        <v>-0.006772109773010015</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Neuron_22</t>
+          <t>Frequency_22</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>9.868479367014515e-08</v>
+        <v>0.02678444981575012</v>
       </c>
       <c r="C24" t="n">
-        <v>0.02559558860957623</v>
+        <v>-0.0186134297400713</v>
       </c>
       <c r="D24" t="n">
-        <v>0.007184114772826433</v>
+        <v>-0.004527891054749489</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Neuron_23</t>
+          <t>Frequency_23</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.150992628457971e-08</v>
+        <v>0.04851849377155304</v>
       </c>
       <c r="C25" t="n">
-        <v>0.01686146110296249</v>
+        <v>-0.03029213845729828</v>
       </c>
       <c r="D25" t="n">
-        <v>0.00494653033092618</v>
+        <v>0.007669744081795216</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Neuron_24</t>
+          <t>Frequency_24</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.752494966922313e-07</v>
+        <v>0.07504252344369888</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.02161144465208054</v>
+        <v>-0.09514042735099792</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0005208940128795803</v>
+        <v>0.01758426800370216</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Neuron_25</t>
+          <t>Frequency_25</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-1.392284048051806e-07</v>
+        <v>0.008048648945987225</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.01244802307337523</v>
+        <v>-0.008373544551432133</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.001143218018114567</v>
+        <v>0.002286990871652961</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Neuron_26</t>
+          <t>Frequency_26</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-1.534482692022721e-07</v>
+        <v>0.02971557341516018</v>
       </c>
       <c r="C28" t="n">
-        <v>0.02156998589634895</v>
+        <v>-0.02329570986330509</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.004483689554035664</v>
+        <v>-0.006947366520762444</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Neuron_27</t>
+          <t>Frequency_27</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.338858481858551e-07</v>
+        <v>-0.1189764216542244</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.06211493909358978</v>
+        <v>-0.05514613166451454</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.01203374844044447</v>
+        <v>-0.006905901711434126</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Neuron_28</t>
+          <t>Frequency_28</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-1.995516356601001e-07</v>
+        <v>0.03246507048606873</v>
       </c>
       <c r="C30" t="n">
-        <v>0.001458982354961336</v>
+        <v>-0.0619313083589077</v>
       </c>
       <c r="D30" t="n">
-        <v>0.003372824983671308</v>
+        <v>-0.01078439503908157</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Neuron_29</t>
+          <t>Frequency_29</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-1.936857785267421e-07</v>
+        <v>0.1795147657394409</v>
       </c>
       <c r="C31" t="n">
-        <v>0.002059274818748236</v>
+        <v>0.05176824331283569</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.001217261073179543</v>
+        <v>-0.006224214565008879</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Neuron_30</t>
+          <t>Frequency_30</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-1.629118173696043e-07</v>
+        <v>-0.1101310178637505</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.001898842747323215</v>
+        <v>-0.1267096698284149</v>
       </c>
       <c r="D32" t="n">
-        <v>0.006390105467289686</v>
+        <v>0.001491776667535305</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Neuron_31</t>
+          <t>Frequency_31</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.181159430847401e-07</v>
+        <v>0.04279816523194313</v>
       </c>
       <c r="C33" t="n">
-        <v>0.04043585062026978</v>
+        <v>0.01795091107487679</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.006896468810737133</v>
+        <v>-0.004031332209706306</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Neuron_32</t>
+          <t>Frequency_32</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>8.557890396332368e-08</v>
+        <v>0.02137590199708939</v>
       </c>
       <c r="C34" t="n">
-        <v>0.004301365464925766</v>
+        <v>-0.04870935156941414</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.004026758950203657</v>
+        <v>-0.005112680606544018</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Neuron_33</t>
+          <t>Frequency_33</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.547522003875201e-07</v>
+        <v>-0.01898201927542686</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.00124504417181015</v>
+        <v>-0.09996204823255539</v>
       </c>
       <c r="D35" t="n">
-        <v>0.001236467505805194</v>
+        <v>-0.003297181101515889</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Neuron_34</t>
+          <t>Frequency_34</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.35605091600155e-07</v>
+        <v>0.06319695711135864</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.01068750396370888</v>
+        <v>0.02805938757956028</v>
       </c>
       <c r="D36" t="n">
-        <v>0.01107252389192581</v>
+        <v>0.002137582981958985</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Neuron_35</t>
+          <t>Frequency_35</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-6.660293649929372e-08</v>
+        <v>0.05788622796535492</v>
       </c>
       <c r="C37" t="n">
-        <v>0.01764084585011005</v>
+        <v>-0.06059369817376137</v>
       </c>
       <c r="D37" t="n">
-        <v>0.001706663751974702</v>
+        <v>0.002686732215806842</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Neuron_36</t>
+          <t>Frequency_36</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2.109056680410504e-07</v>
+        <v>0.09505452215671539</v>
       </c>
       <c r="C38" t="n">
-        <v>0.01540476642549038</v>
+        <v>-0.002827356336638331</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.002796417567878962</v>
+        <v>-0.005584204103797674</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Neuron_37</t>
+          <t>Frequency_37</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.855362796732152e-07</v>
+        <v>-0.2195965349674225</v>
       </c>
       <c r="C39" t="n">
-        <v>0.002903661224991083</v>
+        <v>-0.08254072070121765</v>
       </c>
       <c r="D39" t="n">
-        <v>0.009654249995946884</v>
+        <v>0.005901442840695381</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Neuron_38</t>
+          <t>Frequency_38</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.263119884242769e-07</v>
+        <v>0.1853395402431488</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.01421124581247568</v>
+        <v>0.0003136562008876354</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.009066615253686905</v>
+        <v>0.008986855857074261</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Neuron_39</t>
+          <t>Frequency_39</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.468819021965828e-07</v>
+        <v>0.04515991732478142</v>
       </c>
       <c r="C41" t="n">
-        <v>0.006255180109292269</v>
+        <v>0.03701238334178925</v>
       </c>
       <c r="D41" t="n">
-        <v>0.009512901306152344</v>
+        <v>0.002573562087491155</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Neuron_40</t>
+          <t>Frequency_40</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-8.984719102045347e-08</v>
+        <v>-0.1060962006449699</v>
       </c>
       <c r="C42" t="n">
-        <v>0.01814412325620651</v>
+        <v>-0.03409853205084801</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.001613236614502966</v>
+        <v>0.009091001935303211</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Neuron_41</t>
+          <t>Frequency_41</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-2.396248248714983e-07</v>
+        <v>-0.06025368720293045</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.03917491808533669</v>
+        <v>-0.03033888339996338</v>
       </c>
       <c r="D43" t="n">
-        <v>0.002997979521751404</v>
+        <v>0.004195216577500105</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Neuron_42</t>
+          <t>Frequency_42</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-4.455837654404604e-08</v>
+        <v>-0.03874183818697929</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.00460940133780241</v>
+        <v>0.02855037339031696</v>
       </c>
       <c r="D44" t="n">
-        <v>0.002609193092212081</v>
+        <v>0.005770123563706875</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Neuron_43</t>
+          <t>Frequency_43</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-1.410193277706639e-07</v>
+        <v>0.03628971427679062</v>
       </c>
       <c r="C45" t="n">
-        <v>0.004272988997399807</v>
+        <v>-0.09112267196178436</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.000541769084520638</v>
+        <v>0.004971777088940144</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Neuron_44</t>
+          <t>Frequency_44</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4.668315156663994e-08</v>
+        <v>0.19151471555233</v>
       </c>
       <c r="C46" t="n">
-        <v>0.01044661086052656</v>
+        <v>0.1316365301609039</v>
       </c>
       <c r="D46" t="n">
-        <v>0.004801397211849689</v>
+        <v>-0.002504174597561359</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Neuron_45</t>
+          <t>Frequency_45</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1.634329009903013e-07</v>
+        <v>0.04560325667262077</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.04937857016921043</v>
+        <v>-0.07813417166471481</v>
       </c>
       <c r="D47" t="n">
-        <v>0.004933228250592947</v>
+        <v>0.0001730927469907328</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Neuron_46</t>
+          <t>Frequency_46</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1.281130979080558e-09</v>
+        <v>-0.08132742345333099</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.008788182400166988</v>
+        <v>0.03028145991265774</v>
       </c>
       <c r="D48" t="n">
-        <v>0.006241241469979286</v>
+        <v>0.0008096748497337103</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Neuron_47</t>
+          <t>Frequency_47</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>7.102488552845898e-08</v>
+        <v>0.0282076969742775</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.01391621865332127</v>
+        <v>0.03639402985572815</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.003485169261693954</v>
+        <v>-0.01364567875862122</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Neuron_48</t>
+          <t>Frequency_48</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>7.011957592339968e-08</v>
+        <v>0.1951206922531128</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.01375042647123337</v>
+        <v>0.06126583367586136</v>
       </c>
       <c r="D50" t="n">
-        <v>0.01238903123885393</v>
+        <v>-0.001920221839100122</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Neuron_49</t>
+          <t>Frequency_49</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2.033001749168761e-07</v>
+        <v>-0.1288127899169922</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.02208392322063446</v>
+        <v>-0.09669937193393707</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.002557390136644244</v>
+        <v>-0.001761140068992972</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Neuron_50</t>
+          <t>Frequency_50</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-8.922530980726151e-08</v>
+        <v>-0.002853858051821589</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.01378573663532734</v>
+        <v>-0.06615781784057617</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.003378423629328609</v>
+        <v>-0.006763242650777102</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Neuron_51</t>
+          <t>Frequency_51</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1.505003126567317e-07</v>
+        <v>0.1760005801916122</v>
       </c>
       <c r="C53" t="n">
-        <v>0.02428165450692177</v>
+        <v>0.1018704622983932</v>
       </c>
       <c r="D53" t="n">
-        <v>0.0006569330580532551</v>
+        <v>0.002605830552056432</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Neuron_52</t>
+          <t>Frequency_52</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-1.439926506918709e-07</v>
+        <v>0.1559774577617645</v>
       </c>
       <c r="C54" t="n">
-        <v>0.01340659148991108</v>
+        <v>-0.01043865270912647</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0006314895581454039</v>
+        <v>0.001476586097851396</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Neuron_53</t>
+          <t>Frequency_53</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1.392718207426924e-08</v>
+        <v>0.04317831248044968</v>
       </c>
       <c r="C55" t="n">
-        <v>0.01995690725743771</v>
+        <v>-0.07741346955299377</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.0017891462193802</v>
+        <v>-0.00644002016633749</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Neuron_54</t>
+          <t>Frequency_54</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-1.927399466694624e-07</v>
+        <v>0.1361679285764694</v>
       </c>
       <c r="C56" t="n">
-        <v>0.01502743829041719</v>
+        <v>0.01755610480904579</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.0008049440220929682</v>
+        <v>-0.005385141354054213</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Neuron_55</t>
+          <t>Frequency_55</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>9.253925981056454e-08</v>
+        <v>-0.2757161557674408</v>
       </c>
       <c r="C57" t="n">
-        <v>0.003534474642947316</v>
+        <v>-0.1439376622438431</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.007424852810800076</v>
+        <v>-0.009156332351267338</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Neuron_56</t>
+          <t>Frequency_56</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-3.544643689679106e-08</v>
+        <v>-0.01942571066319942</v>
       </c>
       <c r="C58" t="n">
-        <v>0.006368580739945173</v>
+        <v>-0.03472068533301353</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.006295655388385057</v>
+        <v>-0.001624893746338785</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Neuron_57</t>
+          <t>Frequency_57</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1.337030113290893e-07</v>
+        <v>-0.1666987240314484</v>
       </c>
       <c r="C59" t="n">
-        <v>0.01039855927228928</v>
+        <v>-0.03040311485528946</v>
       </c>
       <c r="D59" t="n">
-        <v>0.004495822358876467</v>
+        <v>0.006913106888532639</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Neuron_58</t>
+          <t>Frequency_58</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-1.901436377238497e-07</v>
+        <v>0.1162810549139977</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.010447490029037</v>
+        <v>0.002286385744810104</v>
       </c>
       <c r="D60" t="n">
-        <v>0.001893485430628061</v>
+        <v>-0.001831277855671942</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Neuron_59</t>
+          <t>Frequency_59</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-1.987485944709988e-07</v>
+        <v>-0.1751824915409088</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.0001652542850933969</v>
+        <v>-0.07671575248241425</v>
       </c>
       <c r="D61" t="n">
-        <v>0.0007278412231244147</v>
+        <v>0.001268844353035092</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Neuron_60</t>
+          <t>Frequency_60</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-9.077376006416671e-08</v>
+        <v>0.04174128547310829</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.006002272944897413</v>
+        <v>0.06699490547180176</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.0006244213436730206</v>
+        <v>-0.00754462368786335</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Neuron_61</t>
+          <t>Frequency_61</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1.441448294059455e-08</v>
+        <v>0.008146298117935658</v>
       </c>
       <c r="C63" t="n">
-        <v>0.002067094435915351</v>
+        <v>-0.04215206950902939</v>
       </c>
       <c r="D63" t="n">
-        <v>0.00836553331464529</v>
+        <v>0.006738301832228899</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Neuron_62</t>
+          <t>Frequency_62</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>5.652946200029874e-08</v>
+        <v>-0.02636521868407726</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.04002048820257187</v>
+        <v>0.03612108901143074</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.00277482601813972</v>
+        <v>0.002437645103782415</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Neuron_63</t>
+          <t>Frequency_63</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-4.316048318742105e-08</v>
+        <v>0.0003347212041262537</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.0756244882941246</v>
+        <v>0.08115386217832565</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.01569378189742565</v>
+        <v>-0.0001743132888805121</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Neuron_64</t>
+          <t>Frequency_64</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-9.979396509152139e-08</v>
+        <v>0.1165144890546799</v>
       </c>
       <c r="C66" t="n">
-        <v>0.000195463711861521</v>
+        <v>0.0198951531201601</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.00123770150821656</v>
+        <v>0.004794309847056866</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Neuron_65</t>
+          <t>Frequency_65</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2.314271618786279e-08</v>
+        <v>0.09715971350669861</v>
       </c>
       <c r="C67" t="n">
-        <v>0.004059541504830122</v>
+        <v>-0.004173589870333672</v>
       </c>
       <c r="D67" t="n">
-        <v>0.0003538978344295174</v>
+        <v>-0.002926216693595052</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Neuron_66</t>
+          <t>Frequency_66</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2.109006658201906e-07</v>
+        <v>0.07998566329479218</v>
       </c>
       <c r="C68" t="n">
-        <v>0.02271624840795994</v>
+        <v>0.1381003558635712</v>
       </c>
       <c r="D68" t="n">
-        <v>0.003548433538526297</v>
+        <v>-0.007432390935719013</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Neuron_67</t>
+          <t>Frequency_67</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1.650791574547839e-07</v>
+        <v>0.1704163998365402</v>
       </c>
       <c r="C69" t="n">
-        <v>0.04933773353695869</v>
+        <v>0.08378922194242477</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.006767132319509983</v>
+        <v>-0.007967476733028889</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Neuron_68</t>
+          <t>Frequency_68</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>6.869341717674615e-08</v>
+        <v>-0.01818990707397461</v>
       </c>
       <c r="C70" t="n">
-        <v>0.007113813422620296</v>
+        <v>0.06974869221448898</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.002022505505010486</v>
+        <v>-0.005284673999994993</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Neuron_69</t>
+          <t>Frequency_69</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.217457565871882e-07</v>
+        <v>-0.09093894809484482</v>
       </c>
       <c r="C71" t="n">
-        <v>0.004669127985835075</v>
+        <v>0.03689600899815559</v>
       </c>
       <c r="D71" t="n">
-        <v>0.0004371335089672357</v>
+        <v>0.008526665158569813</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Neuron_70</t>
+          <t>Frequency_70</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>4.572333978103416e-08</v>
+        <v>-0.09197533875703812</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.01062243711203337</v>
+        <v>0.04609329253435135</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.002043633721768856</v>
+        <v>-0.00750631932169199</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Neuron_71</t>
+          <t>Frequency_71</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1.966277096698832e-07</v>
+        <v>0.3557905554771423</v>
       </c>
       <c r="C73" t="n">
-        <v>0.0100335581228137</v>
+        <v>0.2114708572626114</v>
       </c>
       <c r="D73" t="n">
-        <v>0.003167415736243129</v>
+        <v>0.001396815991029143</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Neuron_72</t>
+          <t>Frequency_72</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1.615329807691523e-07</v>
+        <v>-0.03722731024026871</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.009465905837714672</v>
+        <v>0.0768062025308609</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.0008683899650350213</v>
+        <v>-0.005939494352787733</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Neuron_73</t>
+          <t>Frequency_73</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-2.825468392586572e-08</v>
+        <v>0.104155071079731</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.01195088494569063</v>
+        <v>0.01951391808688641</v>
       </c>
       <c r="D75" t="n">
-        <v>0.003065471537411213</v>
+        <v>-0.003612870816141367</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Neuron_74</t>
+          <t>Frequency_74</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>9.322257454869032e-08</v>
+        <v>-0.1772864907979965</v>
       </c>
       <c r="C76" t="n">
-        <v>-6.02909603912849e-05</v>
+        <v>-0.1328279674053192</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.003144207410514355</v>
+        <v>0.004434977658092976</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Neuron_75</t>
+          <t>Frequency_75</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1.053609395285093e-07</v>
+        <v>0.04039924964308739</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.01765542477369308</v>
+        <v>-0.01687303371727467</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.01450495515018702</v>
+        <v>0.001260136719793081</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Neuron_76</t>
+          <t>Frequency_76</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>3.092891986966606e-08</v>
+        <v>-0.06028307229280472</v>
       </c>
       <c r="C78" t="n">
-        <v>0.035113874822855</v>
+        <v>0.01255108043551445</v>
       </c>
       <c r="D78" t="n">
-        <v>0.0008516069501638412</v>
+        <v>0.002190727740526199</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Neuron_77</t>
+          <t>Frequency_77</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-5.95270073233678e-08</v>
+        <v>0.02726548351347446</v>
       </c>
       <c r="C79" t="n">
-        <v>0.007662021555006504</v>
+        <v>0.01549749914556742</v>
       </c>
       <c r="D79" t="n">
-        <v>0.002228491473942995</v>
+        <v>-0.002309150528162718</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Neuron_78</t>
+          <t>Frequency_78</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1.162605371973768e-07</v>
+        <v>0.1699031442403793</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.02134506031870842</v>
+        <v>0.08976210653781891</v>
       </c>
       <c r="D80" t="n">
-        <v>0.003672032849863172</v>
+        <v>-0.00252040452323854</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Neuron_79</t>
+          <t>Frequency_79</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-9.070475215366969e-08</v>
+        <v>0.1239015758037567</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.05015908181667328</v>
+        <v>0.008637497201561928</v>
       </c>
       <c r="D81" t="n">
-        <v>0.0079276068136096</v>
+        <v>0.01702695712447166</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Neuron_80</t>
+          <t>Frequency_80</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1.24897425735071e-07</v>
+        <v>-0.02517331764101982</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.003312842221930623</v>
+        <v>-0.1074641495943069</v>
       </c>
       <c r="D82" t="n">
-        <v>-0.005798499565571547</v>
+        <v>0.0006903149769641459</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Neuron_81</t>
+          <t>Frequency_81</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>-1.949835706227532e-07</v>
+        <v>-0.1255477070808411</v>
       </c>
       <c r="C83" t="n">
-        <v>0.01999615132808685</v>
+        <v>0.00231664115563035</v>
       </c>
       <c r="D83" t="n">
-        <v>-0.005168579518795013</v>
+        <v>-0.01310982927680016</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Neuron_82</t>
+          <t>Frequency_82</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1.636658595316476e-07</v>
+        <v>0.03080963902175426</v>
       </c>
       <c r="C84" t="n">
-        <v>0.01726222969591618</v>
+        <v>-0.05380221828818321</v>
       </c>
       <c r="D84" t="n">
-        <v>-0.003132138634100556</v>
+        <v>0.003092214465141296</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Neuron_83</t>
+          <t>Frequency_83</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-9.561904334987048e-08</v>
+        <v>0.002852099481970072</v>
       </c>
       <c r="C85" t="n">
-        <v>-0.03410091623663902</v>
+        <v>-0.03761809319257736</v>
       </c>
       <c r="D85" t="n">
-        <v>0.00651585403829813</v>
+        <v>-0.01005776785314083</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Neuron_84</t>
+          <t>Frequency_84</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1.520733547977215e-07</v>
+        <v>0.157444179058075</v>
       </c>
       <c r="C86" t="n">
-        <v>0.03740640729665756</v>
+        <v>0.07791310548782349</v>
       </c>
       <c r="D86" t="n">
-        <v>0.0009002387523651123</v>
+        <v>0.01308271382004023</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Neuron_85</t>
+          <t>Frequency_85</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>-9.348685159338288e-10</v>
+        <v>0.01503401156514883</v>
       </c>
       <c r="C87" t="n">
-        <v>-0.03147876262664795</v>
+        <v>0.130963459610939</v>
       </c>
       <c r="D87" t="n">
-        <v>0.01566650345921516</v>
+        <v>0.003360694739967585</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Neuron_86</t>
+          <t>Frequency_86</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>-7.75015820408953e-08</v>
+        <v>0.07327254861593246</v>
       </c>
       <c r="C88" t="n">
-        <v>-0.006432149559259415</v>
+        <v>-0.07811598479747772</v>
       </c>
       <c r="D88" t="n">
-        <v>-0.003688508877530694</v>
+        <v>-0.0005834547919221222</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Neuron_87</t>
+          <t>Frequency_87</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-1.637367290641123e-07</v>
+        <v>-0.1283862292766571</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.01256397645920515</v>
+        <v>0.0382341593503952</v>
       </c>
       <c r="D89" t="n">
-        <v>0.0042556282132864</v>
+        <v>-0.006226664409041405</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Neuron_88</t>
+          <t>Frequency_88</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>-1.339757744744929e-07</v>
+        <v>-0.1306767910718918</v>
       </c>
       <c r="C90" t="n">
-        <v>-0.02469287440180779</v>
+        <v>-0.00802311860024929</v>
       </c>
       <c r="D90" t="n">
-        <v>0.008099698461592197</v>
+        <v>0.009765093214809895</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Neuron_89</t>
+          <t>Frequency_89</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-1.758142218477587e-07</v>
+        <v>-0.05061823502182961</v>
       </c>
       <c r="C91" t="n">
-        <v>-0.005640024784952402</v>
+        <v>-0.02647904492914677</v>
       </c>
       <c r="D91" t="n">
-        <v>-0.007171135395765305</v>
+        <v>0.005084001459181309</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Neuron_90</t>
+          <t>Frequency_90</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1.691887234755995e-07</v>
+        <v>-0.1317805796861649</v>
       </c>
       <c r="C92" t="n">
-        <v>0.01023782324045897</v>
+        <v>-0.03548630699515343</v>
       </c>
       <c r="D92" t="n">
-        <v>0.003501836443319917</v>
+        <v>0.001100258785299957</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Neuron_91</t>
+          <t>Frequency_91</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1.074342321771837e-07</v>
+        <v>-0.1305143237113953</v>
       </c>
       <c r="C93" t="n">
-        <v>0.001076032407581806</v>
+        <v>-0.0812479555606842</v>
       </c>
       <c r="D93" t="n">
-        <v>0.005362042691558599</v>
+        <v>0.001175343175418675</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Neuron_92</t>
+          <t>Frequency_92</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1.889223000262064e-08</v>
+        <v>-0.08119878172874451</v>
       </c>
       <c r="C94" t="n">
-        <v>0.005661914590746164</v>
+        <v>0.0123444115743041</v>
       </c>
       <c r="D94" t="n">
-        <v>-0.003135363105684519</v>
+        <v>0.002606057561933994</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Neuron_93</t>
+          <t>Frequency_93</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>2.695635359373227e-08</v>
+        <v>0.06872575730085373</v>
       </c>
       <c r="C95" t="n">
-        <v>0.01572876051068306</v>
+        <v>0.02377866767346859</v>
       </c>
       <c r="D95" t="n">
-        <v>-0.01087340246886015</v>
+        <v>-0.003133776132017374</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Neuron_94</t>
+          <t>Frequency_94</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>-1.729243592762941e-07</v>
+        <v>0.2609167695045471</v>
       </c>
       <c r="C96" t="n">
-        <v>0.002620386891067028</v>
+        <v>0.1388908922672272</v>
       </c>
       <c r="D96" t="n">
-        <v>-0.002563911722972989</v>
+        <v>-0.0006039287545718253</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Neuron_95</t>
+          <t>Frequency_95</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>2.840842761031581e-08</v>
+        <v>-0.2028397470712662</v>
       </c>
       <c r="C97" t="n">
-        <v>-0.01198215503245592</v>
+        <v>-0.05264665931463242</v>
       </c>
       <c r="D97" t="n">
-        <v>-0.003059760201722383</v>
+        <v>0.00267410883679986</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Neuron_96</t>
+          <t>Frequency_96</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>6.998417489967323e-08</v>
+        <v>-0.003473147051408887</v>
       </c>
       <c r="C98" t="n">
-        <v>-0.03021272830665112</v>
+        <v>0.08235877007246017</v>
       </c>
       <c r="D98" t="n">
-        <v>0.001460790052078664</v>
+        <v>0.002265601418912411</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Neuron_97</t>
+          <t>Frequency_97</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>8.468130374694738e-08</v>
+        <v>-0.05760431662201881</v>
       </c>
       <c r="C99" t="n">
-        <v>0.03979146480560303</v>
+        <v>-0.03308651223778725</v>
       </c>
       <c r="D99" t="n">
-        <v>-0.005138426553457975</v>
+        <v>0.01226937398314476</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Neuron_98</t>
+          <t>Frequency_98</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>-1.914662419721935e-07</v>
+        <v>0.3144049346446991</v>
       </c>
       <c r="C100" t="n">
-        <v>-9.55216892180033e-05</v>
+        <v>0.1761250793933868</v>
       </c>
       <c r="D100" t="n">
-        <v>-0.001657661166973412</v>
+        <v>0.001001409254968166</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Neuron_99</t>
+          <t>Frequency_99</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>-1.242382836608158e-07</v>
+        <v>-0.1363033950328827</v>
       </c>
       <c r="C101" t="n">
-        <v>-0.008564585819840431</v>
+        <v>-0.02709869481623173</v>
       </c>
       <c r="D101" t="n">
-        <v>0.001769330468960106</v>
+        <v>0.01116379350423813</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Neuron_100</t>
+          <t>Frequency_100</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>1.118315395842728e-07</v>
+        <v>0.06807950884103775</v>
       </c>
       <c r="C102" t="n">
-        <v>-0.011629993095994</v>
+        <v>-0.07515110075473785</v>
       </c>
       <c r="D102" t="n">
-        <v>-0.00238357437774539</v>
+        <v>-0.008484148420393467</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Neuron_101</t>
+          <t>Frequency_101</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>1.07576504149165e-07</v>
+        <v>0.01366443745791912</v>
       </c>
       <c r="C103" t="n">
-        <v>0.02830968983471394</v>
+        <v>0.06666252017021179</v>
       </c>
       <c r="D103" t="n">
-        <v>-0.01171484030783176</v>
+        <v>0.002895640674978495</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Neuron_102</t>
+          <t>Frequency_102</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>-5.616570319944003e-08</v>
+        <v>0.1666470617055893</v>
       </c>
       <c r="C104" t="n">
-        <v>-0.001993932528421283</v>
+        <v>0.01066738553345203</v>
       </c>
       <c r="D104" t="n">
-        <v>0.0064092050306499</v>
+        <v>0.001475087832659483</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Neuron_103</t>
+          <t>Frequency_103</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>8.969873022124375e-08</v>
+        <v>0.01233770232647657</v>
       </c>
       <c r="C105" t="n">
-        <v>0.03262845799326897</v>
+        <v>0.07199858874082565</v>
       </c>
       <c r="D105" t="n">
-        <v>0.01429613865911961</v>
+        <v>-0.002408357569947839</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Neuron_104</t>
+          <t>Frequency_104</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>-8.467265999456686e-09</v>
+        <v>-0.1011489257216454</v>
       </c>
       <c r="C106" t="n">
-        <v>-0.02480077929794788</v>
+        <v>-0.04999281466007233</v>
       </c>
       <c r="D106" t="n">
-        <v>-0.001488079084083438</v>
+        <v>0.007676825858652592</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Neuron_105</t>
+          <t>Frequency_105</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>-6.801658969379787e-08</v>
+        <v>-0.1009337455034256</v>
       </c>
       <c r="C107" t="n">
-        <v>0.003736539976671338</v>
+        <v>0.01703533343970776</v>
       </c>
       <c r="D107" t="n">
-        <v>-0.008111990988254547</v>
+        <v>0.00369172845967114</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Neuron_106</t>
+          <t>Frequency_106</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>-1.05496880564715e-07</v>
+        <v>0.09317895025014877</v>
       </c>
       <c r="C108" t="n">
-        <v>0.01683791726827621</v>
+        <v>0.03690335899591446</v>
       </c>
       <c r="D108" t="n">
-        <v>0.00247075455263257</v>
+        <v>0.009131528437137604</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Neuron_107</t>
+          <t>Frequency_107</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>7.932722922987523e-08</v>
+        <v>0.1376195251941681</v>
       </c>
       <c r="C109" t="n">
-        <v>-0.007422009948641062</v>
+        <v>0.1082147657871246</v>
       </c>
       <c r="D109" t="n">
-        <v>0.002910285256803036</v>
+        <v>-0.002359844278544188</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Neuron_108</t>
+          <t>Frequency_108</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>-1.974041481389577e-07</v>
+        <v>-0.07112203538417816</v>
       </c>
       <c r="C110" t="n">
-        <v>0.01540351659059525</v>
+        <v>-0.03307867422699928</v>
       </c>
       <c r="D110" t="n">
-        <v>-0.005625086836516857</v>
+        <v>-0.00725479843094945</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Neuron_109</t>
+          <t>Frequency_109</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>1.654928780681075e-07</v>
+        <v>-0.1930266916751862</v>
       </c>
       <c r="C111" t="n">
-        <v>-0.005561497993767262</v>
+        <v>-0.07062026858329773</v>
       </c>
       <c r="D111" t="n">
-        <v>0.001732931821607053</v>
+        <v>0.003265941981226206</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Neuron_110</t>
+          <t>Frequency_110</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>-1.872949155767856e-07</v>
+        <v>-0.1505411267280579</v>
       </c>
       <c r="C112" t="n">
-        <v>0.009168339893221855</v>
+        <v>-0.03981849923729897</v>
       </c>
       <c r="D112" t="n">
-        <v>0.005246401764452457</v>
+        <v>-0.007022089790552855</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Neuron_111</t>
+          <t>Frequency_111</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>-1.513779857020836e-08</v>
+        <v>-0.09361962974071503</v>
       </c>
       <c r="C113" t="n">
-        <v>-0.02053848095238209</v>
+        <v>0.0387532003223896</v>
       </c>
       <c r="D113" t="n">
-        <v>-0.0007827212102711201</v>
+        <v>0.0006796595407649875</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Neuron_112</t>
+          <t>Frequency_112</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>7.224430476071575e-08</v>
+        <v>0.001482266350649297</v>
       </c>
       <c r="C114" t="n">
-        <v>-0.0006813177024014294</v>
+        <v>-0.04840056970715523</v>
       </c>
       <c r="D114" t="n">
-        <v>0.005345194134861231</v>
+        <v>-0.0001773507829057053</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Neuron_113</t>
+          <t>Frequency_113</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>-1.178842552462811e-07</v>
+        <v>-0.01607401855289936</v>
       </c>
       <c r="C115" t="n">
-        <v>0.01580410823225975</v>
+        <v>-0.1388827562332153</v>
       </c>
       <c r="D115" t="n">
-        <v>0.005624927580356598</v>
+        <v>0.00341427861712873</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Neuron_114</t>
+          <t>Frequency_114</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>-4.544193643596373e-08</v>
+        <v>0.2001269459724426</v>
       </c>
       <c r="C116" t="n">
-        <v>-3.252753231208771e-06</v>
+        <v>0.06618249416351318</v>
       </c>
       <c r="D116" t="n">
-        <v>0.003497890895232558</v>
+        <v>0.007203121669590473</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Neuron_115</t>
+          <t>Frequency_115</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>-2.597534098924825e-08</v>
+        <v>-0.05622681230306625</v>
       </c>
       <c r="C117" t="n">
-        <v>-0.0333281047642231</v>
+        <v>0.01396783068776131</v>
       </c>
       <c r="D117" t="n">
-        <v>0.002819236600771546</v>
+        <v>-0.009447165764868259</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Neuron_116</t>
+          <t>Frequency_116</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>-1.593001286437357e-07</v>
+        <v>0.09349163621664047</v>
       </c>
       <c r="C118" t="n">
-        <v>-0.01045131031423807</v>
+        <v>-0.008745110593736172</v>
       </c>
       <c r="D118" t="n">
-        <v>-0.006080557126551867</v>
+        <v>0.001525077037513256</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Neuron_117</t>
+          <t>Frequency_117</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>-2.127919742633821e-07</v>
+        <v>-0.01621721498668194</v>
       </c>
       <c r="C119" t="n">
-        <v>-0.01087351609021425</v>
+        <v>0.08966002613306046</v>
       </c>
       <c r="D119" t="n">
-        <v>-0.005994852632284164</v>
+        <v>-0.001990207470953465</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Neuron_118</t>
+          <t>Frequency_118</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>1.287857998022446e-07</v>
+        <v>-0.1491632461547852</v>
       </c>
       <c r="C120" t="n">
-        <v>0.007358478382229805</v>
+        <v>-0.02183764986693859</v>
       </c>
       <c r="D120" t="n">
-        <v>0.007999125868082047</v>
+        <v>-0.003378839930519462</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Neuron_119</t>
+          <t>Frequency_119</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>-1.20018786020637e-08</v>
+        <v>0.1062607616186142</v>
       </c>
       <c r="C121" t="n">
-        <v>-0.009972228668630123</v>
+        <v>0.01335173472762108</v>
       </c>
       <c r="D121" t="n">
-        <v>0.001316368114203215</v>
+        <v>-0.002099428325891495</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Neuron_120</t>
+          <t>Frequency_120</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>-1.525937420865375e-07</v>
+        <v>-0.03270739689469337</v>
       </c>
       <c r="C122" t="n">
-        <v>0.01521044131368399</v>
+        <v>0.1078458577394485</v>
       </c>
       <c r="D122" t="n">
-        <v>0.0008086301968432963</v>
+        <v>-0.004087853245437145</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Neuron_121</t>
+          <t>Frequency_121</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>-5.885436138441946e-08</v>
+        <v>-0.01321235671639442</v>
       </c>
       <c r="C123" t="n">
-        <v>-0.004780187271535397</v>
+        <v>0.05086918920278549</v>
       </c>
       <c r="D123" t="n">
-        <v>-0.001263945829123259</v>
+        <v>-0.003112826030701399</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Neuron_122</t>
+          <t>Frequency_122</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>6.859191614694282e-08</v>
+        <v>0.101360596716404</v>
       </c>
       <c r="C124" t="n">
-        <v>0.01991062052547932</v>
+        <v>0.08462797105312347</v>
       </c>
       <c r="D124" t="n">
-        <v>0.001063250005245209</v>
+        <v>0.0002149413630831987</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Neuron_123</t>
+          <t>Frequency_123</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>-4.233595873870399e-08</v>
+        <v>-0.1391045749187469</v>
       </c>
       <c r="C125" t="n">
-        <v>0.03500344231724739</v>
+        <v>0.01538321375846863</v>
       </c>
       <c r="D125" t="n">
-        <v>-0.006084267515689135</v>
+        <v>-0.006179040297865868</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Neuron_124</t>
+          <t>Frequency_124</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>-6.661637286242694e-08</v>
+        <v>-0.01942826621234417</v>
       </c>
       <c r="C126" t="n">
-        <v>0.01212123595178127</v>
+        <v>-0.06928543746471405</v>
       </c>
       <c r="D126" t="n">
-        <v>-0.005808934569358826</v>
+        <v>0.005432148929685354</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Neuron_125</t>
+          <t>Frequency_125</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>6.859515622181789e-08</v>
+        <v>0.07771488279104233</v>
       </c>
       <c r="C127" t="n">
-        <v>0.05611544102430344</v>
+        <v>0.05076057463884354</v>
       </c>
       <c r="D127" t="n">
-        <v>0.008169614709913731</v>
+        <v>0.01534496527165174</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Neuron_126</t>
+          <t>Frequency_126</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>-1.366095716548443e-07</v>
+        <v>0.06060594692826271</v>
       </c>
       <c r="C128" t="n">
-        <v>0.01493884157389402</v>
+        <v>0.08950603008270264</v>
       </c>
       <c r="D128" t="n">
-        <v>-0.002121416386216879</v>
+        <v>-0.0005608000210486352</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Neuron_127</t>
+          <t>Frequency_127</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>2.25921397145612e-08</v>
+        <v>0.1511973142623901</v>
       </c>
       <c r="C129" t="n">
-        <v>0.005027350503951311</v>
+        <v>0.07122813165187836</v>
       </c>
       <c r="D129" t="n">
-        <v>-0.001026084646582603</v>
+        <v>-0.001335176406428218</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Frequency_128</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>0.05422114580869675</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.00313817011192441</v>
+      </c>
+      <c r="D130" t="n">
+        <v>-0.00834268145263195</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Frequency_129</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>0.0034158187918365</v>
+      </c>
+      <c r="C131" t="n">
+        <v>-0.05767566338181496</v>
+      </c>
+      <c r="D131" t="n">
+        <v>-0.002007464179769158</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Frequency_130</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>0.03461160883307457</v>
+      </c>
+      <c r="C132" t="n">
+        <v>-0.02660876139998436</v>
+      </c>
+      <c r="D132" t="n">
+        <v>-0.004563945811241865</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Frequency_131</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>0.1119411513209343</v>
+      </c>
+      <c r="C133" t="n">
+        <v>-0.05449754372239113</v>
+      </c>
+      <c r="D133" t="n">
+        <v>-0.000973583897575736</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Frequency_132</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>0.1029026359319687</v>
+      </c>
+      <c r="C134" t="n">
+        <v>-0.0192199032753706</v>
+      </c>
+      <c r="D134" t="n">
+        <v>-0.006655477918684483</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Frequency_133</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>-0.1578065901994705</v>
+      </c>
+      <c r="C135" t="n">
+        <v>-0.08525440841913223</v>
+      </c>
+      <c r="D135" t="n">
+        <v>-0.001515656244009733</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Frequency_134</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>0.02713846042752266</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.1681467592716217</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.007801805157214403</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Frequency_135</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>0.04603463783860207</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.03931263461709023</v>
+      </c>
+      <c r="D137" t="n">
+        <v>-0.006428787019103765</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Frequency_136</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>-0.01609548553824425</v>
+      </c>
+      <c r="C138" t="n">
+        <v>-0.095276840031147</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.003122232155874372</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Frequency_137</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>-0.1283886283636093</v>
+      </c>
+      <c r="C139" t="n">
+        <v>-0.007671407423913479</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.006323824170976877</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Frequency_138</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>0.0982808843255043</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.05856679007411003</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.008209087885916233</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Frequency_139</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>0.008297046646475792</v>
+      </c>
+      <c r="C141" t="n">
+        <v>-0.02895917743444443</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.003689124481752515</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Frequency_140</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>0.06221321597695351</v>
+      </c>
+      <c r="C142" t="n">
+        <v>-0.01172109134495258</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.004145320970565081</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Frequency_141</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>-0.2045701891183853</v>
+      </c>
+      <c r="C143" t="n">
+        <v>-0.1173113361001015</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.001601890660822392</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Frequency_142</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>0.02860978618264198</v>
+      </c>
+      <c r="C144" t="n">
+        <v>0.05114224925637245</v>
+      </c>
+      <c r="D144" t="n">
+        <v>0.007971231825649738</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Frequency_143</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>0.001414719736203551</v>
+      </c>
+      <c r="C145" t="n">
+        <v>0.0261544045060873</v>
+      </c>
+      <c r="D145" t="n">
+        <v>0.00260511483065784</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Frequency_144</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>-0.1214968636631966</v>
+      </c>
+      <c r="C146" t="n">
+        <v>-0.08889873325824738</v>
+      </c>
+      <c r="D146" t="n">
+        <v>-0.003702540881931782</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Frequency_145</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>0.1346420049667358</v>
+      </c>
+      <c r="C147" t="n">
+        <v>0.0223202146589756</v>
+      </c>
+      <c r="D147" t="n">
+        <v>0.0001181353582069278</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Frequency_146</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>-0.1050054207444191</v>
+      </c>
+      <c r="C148" t="n">
+        <v>-0.004974976647645235</v>
+      </c>
+      <c r="D148" t="n">
+        <v>0.002116891089826822</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Frequency_147</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>0.01574782282114029</v>
+      </c>
+      <c r="C149" t="n">
+        <v>-0.1440620422363281</v>
+      </c>
+      <c r="D149" t="n">
+        <v>-3.572100831661373e-05</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Frequency_148</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>-0.003823685692623258</v>
+      </c>
+      <c r="C150" t="n">
+        <v>0.04704676941037178</v>
+      </c>
+      <c r="D150" t="n">
+        <v>0.00476021645590663</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Frequency_149</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>-0.1382336318492889</v>
+      </c>
+      <c r="C151" t="n">
+        <v>-0.004047387279570103</v>
+      </c>
+      <c r="D151" t="n">
+        <v>0.006002978887408972</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Frequency_150</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>0.1139557585120201</v>
+      </c>
+      <c r="C152" t="n">
+        <v>-0.03575263917446136</v>
+      </c>
+      <c r="D152" t="n">
+        <v>-0.002473997417837381</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Frequency_151</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>-0.174754410982132</v>
+      </c>
+      <c r="C153" t="n">
+        <v>-0.04920397698879242</v>
+      </c>
+      <c r="D153" t="n">
+        <v>-0.003503041807562113</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Frequency_152</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>-0.05515866726636887</v>
+      </c>
+      <c r="C154" t="n">
+        <v>0.0001648483594181016</v>
+      </c>
+      <c r="D154" t="n">
+        <v>-0.00795879028737545</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Frequency_153</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>0.06144324317574501</v>
+      </c>
+      <c r="C155" t="n">
+        <v>-0.01924856007099152</v>
+      </c>
+      <c r="D155" t="n">
+        <v>-0.00116862915456295</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Frequency_154</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>-0.164644181728363</v>
+      </c>
+      <c r="C156" t="n">
+        <v>0.01167674735188484</v>
+      </c>
+      <c r="D156" t="n">
+        <v>0.005025253165513277</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Frequency_155</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>0.04357726126909256</v>
+      </c>
+      <c r="C157" t="n">
+        <v>0.07363680005073547</v>
+      </c>
+      <c r="D157" t="n">
+        <v>0.007952284067869186</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Frequency_156</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>0.05149873346090317</v>
+      </c>
+      <c r="C158" t="n">
+        <v>-0.02492799982428551</v>
+      </c>
+      <c r="D158" t="n">
+        <v>0.01030673366039991</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Frequency_157</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>0.1720705181360245</v>
+      </c>
+      <c r="C159" t="n">
+        <v>0.0241842046380043</v>
+      </c>
+      <c r="D159" t="n">
+        <v>-0.002014349680393934</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Frequency_158</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>-0.1134786605834961</v>
+      </c>
+      <c r="C160" t="n">
+        <v>-0.02997769601643085</v>
+      </c>
+      <c r="D160" t="n">
+        <v>-0.0004411949776113033</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Frequency_159</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>0.1875314563512802</v>
+      </c>
+      <c r="C161" t="n">
+        <v>0.08699923008680344</v>
+      </c>
+      <c r="D161" t="n">
+        <v>-0.004366188310086727</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Frequency_160</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>0.140273317694664</v>
+      </c>
+      <c r="C162" t="n">
+        <v>0.008017087355256081</v>
+      </c>
+      <c r="D162" t="n">
+        <v>0.009483695961534977</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Frequency_161</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>0.07879295945167542</v>
+      </c>
+      <c r="C163" t="n">
+        <v>0.05107320845127106</v>
+      </c>
+      <c r="D163" t="n">
+        <v>0.007439513225108385</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Frequency_162</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>0.2572054862976074</v>
+      </c>
+      <c r="C164" t="n">
+        <v>0.1291371881961823</v>
+      </c>
+      <c r="D164" t="n">
+        <v>0.005830585956573486</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Frequency_163</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>0.09377524256706238</v>
+      </c>
+      <c r="C165" t="n">
+        <v>0.03598000854253769</v>
+      </c>
+      <c r="D165" t="n">
+        <v>-3.709865268319845e-05</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Frequency_164</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>-0.07160390913486481</v>
+      </c>
+      <c r="C166" t="n">
+        <v>0.01207469683140516</v>
+      </c>
+      <c r="D166" t="n">
+        <v>0.01044682879000902</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Frequency_165</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>-0.100727804005146</v>
+      </c>
+      <c r="C167" t="n">
+        <v>0.01720351353287697</v>
+      </c>
+      <c r="D167" t="n">
+        <v>0.008113536983728409</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Frequency_166</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>0.07247579097747803</v>
+      </c>
+      <c r="C168" t="n">
+        <v>-0.08942300081253052</v>
+      </c>
+      <c r="D168" t="n">
+        <v>-0.0006857581902295351</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Frequency_167</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>-0.03427350521087646</v>
+      </c>
+      <c r="C169" t="n">
+        <v>-0.1673081964254379</v>
+      </c>
+      <c r="D169" t="n">
+        <v>-0.0007845748914405704</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Frequency_168</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>0.01392960362136364</v>
+      </c>
+      <c r="C170" t="n">
+        <v>0.1451932787895203</v>
+      </c>
+      <c r="D170" t="n">
+        <v>0.01045768335461617</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Frequency_169</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>0.09729418903589249</v>
+      </c>
+      <c r="C171" t="n">
+        <v>0.1335117071866989</v>
+      </c>
+      <c r="D171" t="n">
+        <v>0.0001016201786114834</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Frequency_170</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>0.002449482213705778</v>
+      </c>
+      <c r="C172" t="n">
+        <v>0.03142079710960388</v>
+      </c>
+      <c r="D172" t="n">
+        <v>-0.005174426827579737</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Frequency_171</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>-0.03519158810377121</v>
+      </c>
+      <c r="C173" t="n">
+        <v>-0.02933182753622532</v>
+      </c>
+      <c r="D173" t="n">
+        <v>0.01522975042462349</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Frequency_172</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>0.0646001473069191</v>
+      </c>
+      <c r="C174" t="n">
+        <v>-0.06154952943325043</v>
+      </c>
+      <c r="D174" t="n">
+        <v>0.005827099550515413</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Frequency_173</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>0.1094422489404678</v>
+      </c>
+      <c r="C175" t="n">
+        <v>0.063064806163311</v>
+      </c>
+      <c r="D175" t="n">
+        <v>0.003834591712802649</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Frequency_174</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>0.002725638449192047</v>
+      </c>
+      <c r="C176" t="n">
+        <v>0.008079317398369312</v>
+      </c>
+      <c r="D176" t="n">
+        <v>-0.001106612617149949</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Frequency_175</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>0.2202349007129669</v>
+      </c>
+      <c r="C177" t="n">
+        <v>0.09278812259435654</v>
+      </c>
+      <c r="D177" t="n">
+        <v>-0.008146578446030617</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Frequency_176</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>-0.1849689185619354</v>
+      </c>
+      <c r="C178" t="n">
+        <v>-0.1532273441553116</v>
+      </c>
+      <c r="D178" t="n">
+        <v>0.001880299765616655</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Frequency_177</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>-0.07596319913864136</v>
+      </c>
+      <c r="C179" t="n">
+        <v>-0.06813618540763855</v>
+      </c>
+      <c r="D179" t="n">
+        <v>-0.001219699741341174</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Frequency_178</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>0.1675501763820648</v>
+      </c>
+      <c r="C180" t="n">
+        <v>0.04208735749125481</v>
+      </c>
+      <c r="D180" t="n">
+        <v>0.00801478698849678</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Frequency_179</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>0.05657732114195824</v>
+      </c>
+      <c r="C181" t="n">
+        <v>-0.002258234191685915</v>
+      </c>
+      <c r="D181" t="n">
+        <v>0.001975852996110916</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Frequency_180</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>0.1329174190759659</v>
+      </c>
+      <c r="C182" t="n">
+        <v>0.03052420727908611</v>
+      </c>
+      <c r="D182" t="n">
+        <v>-0.00336410291492939</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Frequency_181</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>-0.11995580047369</v>
+      </c>
+      <c r="C183" t="n">
+        <v>0.03288837522268295</v>
+      </c>
+      <c r="D183" t="n">
+        <v>-0.003319598035886884</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Frequency_182</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>0.1424980163574219</v>
+      </c>
+      <c r="C184" t="n">
+        <v>0.06626059859991074</v>
+      </c>
+      <c r="D184" t="n">
+        <v>0.009659205563366413</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Frequency_183</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>0.2102135270833969</v>
+      </c>
+      <c r="C185" t="n">
+        <v>0.1031136736273766</v>
+      </c>
+      <c r="D185" t="n">
+        <v>0.007720803841948509</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Frequency_184</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>-0.121639795601368</v>
+      </c>
+      <c r="C186" t="n">
+        <v>-0.0597720593214035</v>
+      </c>
+      <c r="D186" t="n">
+        <v>-0.0004284176102373749</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Frequency_185</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>0.07832858711481094</v>
+      </c>
+      <c r="C187" t="n">
+        <v>0.03718119487166405</v>
+      </c>
+      <c r="D187" t="n">
+        <v>-0.003235985757783055</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Frequency_186</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>-0.0567479282617569</v>
+      </c>
+      <c r="C188" t="n">
+        <v>-0.0180713664740324</v>
+      </c>
+      <c r="D188" t="n">
+        <v>-3.24530410580337e-05</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Frequency_187</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>0.08249407261610031</v>
+      </c>
+      <c r="C189" t="n">
+        <v>0.02326708287000656</v>
+      </c>
+      <c r="D189" t="n">
+        <v>-0.0004295014659874141</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Frequency_188</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>-0.1841675490140915</v>
+      </c>
+      <c r="C190" t="n">
+        <v>-0.0878819152712822</v>
+      </c>
+      <c r="D190" t="n">
+        <v>-0.008598190732300282</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Frequency_189</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>0.1407504230737686</v>
+      </c>
+      <c r="C191" t="n">
+        <v>0.1029602140188217</v>
+      </c>
+      <c r="D191" t="n">
+        <v>0.0116368755698204</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Frequency_190</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>0.01064666733145714</v>
+      </c>
+      <c r="C192" t="n">
+        <v>-0.08116798847913742</v>
+      </c>
+      <c r="D192" t="n">
+        <v>-0.000331022369209677</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Frequency_191</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>-0.08580633997917175</v>
+      </c>
+      <c r="C193" t="n">
+        <v>0.02243431285023689</v>
+      </c>
+      <c r="D193" t="n">
+        <v>0.007007459178566933</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Frequency_192</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>-0.06283523142337799</v>
+      </c>
+      <c r="C194" t="n">
+        <v>0.05819811299443245</v>
+      </c>
+      <c r="D194" t="n">
+        <v>-0.009074844419956207</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Frequency_193</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>-0.1066912412643433</v>
+      </c>
+      <c r="C195" t="n">
+        <v>-0.05354009196162224</v>
+      </c>
+      <c r="D195" t="n">
+        <v>-0.01111625600606203</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Frequency_194</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>0.1140772700309753</v>
+      </c>
+      <c r="C196" t="n">
+        <v>-0.0590655691921711</v>
+      </c>
+      <c r="D196" t="n">
+        <v>-0.003741960506886244</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Frequency_195</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>0.03115848265588284</v>
+      </c>
+      <c r="C197" t="n">
+        <v>-0.08439719676971436</v>
+      </c>
+      <c r="D197" t="n">
+        <v>-0.005499079823493958</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Frequency_196</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>0.1139700561761856</v>
+      </c>
+      <c r="C198" t="n">
+        <v>0.04193898290395737</v>
+      </c>
+      <c r="D198" t="n">
+        <v>0.001752491691149771</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Frequency_197</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>0.1714169383049011</v>
+      </c>
+      <c r="C199" t="n">
+        <v>0.04545166343450546</v>
+      </c>
+      <c r="D199" t="n">
+        <v>0.001936280401423573</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Frequency_198</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>-0.04566251486539841</v>
+      </c>
+      <c r="C200" t="n">
+        <v>-0.01491806656122208</v>
+      </c>
+      <c r="D200" t="n">
+        <v>0.008820801042020321</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Frequency_199</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>0.1157010644674301</v>
+      </c>
+      <c r="C201" t="n">
+        <v>0.09346006065607071</v>
+      </c>
+      <c r="D201" t="n">
+        <v>0.01100530568510294</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Frequency_200</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>-0.1052723303437233</v>
+      </c>
+      <c r="C202" t="n">
+        <v>0.04403926804661751</v>
+      </c>
+      <c r="D202" t="n">
+        <v>-0.004693458788096905</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Frequency_201</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>0.08235851675271988</v>
+      </c>
+      <c r="C203" t="n">
+        <v>-0.0008948575123213232</v>
+      </c>
+      <c r="D203" t="n">
+        <v>0.009784610010683537</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Frequency_202</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>-0.1081316098570824</v>
+      </c>
+      <c r="C204" t="n">
+        <v>-0.02957838401198387</v>
+      </c>
+      <c r="D204" t="n">
+        <v>0.001710500102490187</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Frequency_203</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>-0.08324230462312698</v>
+      </c>
+      <c r="C205" t="n">
+        <v>0.05385719612240791</v>
+      </c>
+      <c r="D205" t="n">
+        <v>0.007228691596537828</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Frequency_204</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>0.1094454973936081</v>
+      </c>
+      <c r="C206" t="n">
+        <v>0.02581628039479256</v>
+      </c>
+      <c r="D206" t="n">
+        <v>-0.006577021442353725</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Frequency_205</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>-0.1669141501188278</v>
+      </c>
+      <c r="C207" t="n">
+        <v>-0.02665264159440994</v>
+      </c>
+      <c r="D207" t="n">
+        <v>0.001625902368687093</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Frequency_206</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>0.1100977286696434</v>
+      </c>
+      <c r="C208" t="n">
+        <v>0.09518393874168396</v>
+      </c>
+      <c r="D208" t="n">
+        <v>0.009740386158227921</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Frequency_207</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>0.2161026895046234</v>
+      </c>
+      <c r="C209" t="n">
+        <v>0.1068002432584763</v>
+      </c>
+      <c r="D209" t="n">
+        <v>0.004760110285133123</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Frequency_208</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>-0.02863269485533237</v>
+      </c>
+      <c r="C210" t="n">
+        <v>-0.03067120350897312</v>
+      </c>
+      <c r="D210" t="n">
+        <v>0.006884502246975899</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Frequency_209</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>-0.1154051125049591</v>
+      </c>
+      <c r="C211" t="n">
+        <v>0.01100811082869768</v>
+      </c>
+      <c r="D211" t="n">
+        <v>-0.0001965734409168363</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Frequency_210</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>0.07228904962539673</v>
+      </c>
+      <c r="C212" t="n">
+        <v>-0.05241459235548973</v>
+      </c>
+      <c r="D212" t="n">
+        <v>0.003088273573666811</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Frequency_211</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>-0.05809080600738525</v>
+      </c>
+      <c r="C213" t="n">
+        <v>-0.04209494963288307</v>
+      </c>
+      <c r="D213" t="n">
+        <v>-0.009451991878449917</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Frequency_212</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>0.2160765528678894</v>
+      </c>
+      <c r="C214" t="n">
+        <v>0.04946260899305344</v>
+      </c>
+      <c r="D214" t="n">
+        <v>0.007052266970276833</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Frequency_213</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>-0.2053903192281723</v>
+      </c>
+      <c r="C215" t="n">
+        <v>-0.1055571660399437</v>
+      </c>
+      <c r="D215" t="n">
+        <v>0.008648227900266647</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Frequency_214</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>-0.2098222970962524</v>
+      </c>
+      <c r="C216" t="n">
+        <v>-0.1096299514174461</v>
+      </c>
+      <c r="D216" t="n">
+        <v>-0.004292172845453024</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Frequency_215</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>0.08522520214319229</v>
+      </c>
+      <c r="C217" t="n">
+        <v>-0.01337331905961037</v>
+      </c>
+      <c r="D217" t="n">
+        <v>0.003355268156155944</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Frequency_216</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>0.129967987537384</v>
+      </c>
+      <c r="C218" t="n">
+        <v>0.01260140538215637</v>
+      </c>
+      <c r="D218" t="n">
+        <v>0.0074295774102211</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Frequency_217</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>-0.06050009280443192</v>
+      </c>
+      <c r="C219" t="n">
+        <v>-0.008361861109733582</v>
+      </c>
+      <c r="D219" t="n">
+        <v>-0.004558077082037926</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Frequency_218</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>0.04929238557815552</v>
+      </c>
+      <c r="C220" t="n">
+        <v>0.02007379569113255</v>
+      </c>
+      <c r="D220" t="n">
+        <v>0.0005960114067420363</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Frequency_219</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>-0.07745435833930969</v>
+      </c>
+      <c r="C221" t="n">
+        <v>-0.1574942618608475</v>
+      </c>
+      <c r="D221" t="n">
+        <v>-0.006169448606669903</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Frequency_220</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>-0.3047455251216888</v>
+      </c>
+      <c r="C222" t="n">
+        <v>-0.1668847501277924</v>
+      </c>
+      <c r="D222" t="n">
+        <v>-0.003112594364210963</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Frequency_221</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>0.01174858212471008</v>
+      </c>
+      <c r="C223" t="n">
+        <v>0.1546235382556915</v>
+      </c>
+      <c r="D223" t="n">
+        <v>-0.009897688403725624</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Frequency_222</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>0.2096724063158035</v>
+      </c>
+      <c r="C224" t="n">
+        <v>0.06661824882030487</v>
+      </c>
+      <c r="D224" t="n">
+        <v>0.004808468278497458</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Frequency_223</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>-0.04834134131669998</v>
+      </c>
+      <c r="C225" t="n">
+        <v>-0.07414691150188446</v>
+      </c>
+      <c r="D225" t="n">
+        <v>0.001005860744044185</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Frequency_224</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>0.1345389485359192</v>
+      </c>
+      <c r="C226" t="n">
+        <v>0.03183213621377945</v>
+      </c>
+      <c r="D226" t="n">
+        <v>-0.00193990720435977</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Frequency_225</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>0.02251919358968735</v>
+      </c>
+      <c r="C227" t="n">
+        <v>0.07172895222902298</v>
+      </c>
+      <c r="D227" t="n">
+        <v>-0.0007127805147320032</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Frequency_226</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>-0.05194792896509171</v>
+      </c>
+      <c r="C228" t="n">
+        <v>-0.03616267070174217</v>
+      </c>
+      <c r="D228" t="n">
+        <v>0.00088880630210042</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Frequency_227</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>0.12303526699543</v>
+      </c>
+      <c r="C229" t="n">
+        <v>0.2032008618116379</v>
+      </c>
+      <c r="D229" t="n">
+        <v>0.0009513528784736991</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Frequency_228</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>-0.1825998574495316</v>
+      </c>
+      <c r="C230" t="n">
+        <v>-0.0974615067243576</v>
+      </c>
+      <c r="D230" t="n">
+        <v>0.006276735570281744</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Frequency_229</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>-0.1172851994633675</v>
+      </c>
+      <c r="C231" t="n">
+        <v>-0.1483174264431</v>
+      </c>
+      <c r="D231" t="n">
+        <v>0.009495066478848457</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Frequency_230</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>0.1100075840950012</v>
+      </c>
+      <c r="C232" t="n">
+        <v>-0.0171081181615591</v>
+      </c>
+      <c r="D232" t="n">
+        <v>0.0005967368488200009</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Frequency_231</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>0.02929537743330002</v>
+      </c>
+      <c r="C233" t="n">
+        <v>-0.06213733553886414</v>
+      </c>
+      <c r="D233" t="n">
+        <v>0.01125174481421709</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Frequency_232</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>0.04071157425642014</v>
+      </c>
+      <c r="C234" t="n">
+        <v>0.01631792075932026</v>
+      </c>
+      <c r="D234" t="n">
+        <v>-0.006857680156826973</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Frequency_233</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>0.03180064260959625</v>
+      </c>
+      <c r="C235" t="n">
+        <v>-0.04457613080739975</v>
+      </c>
+      <c r="D235" t="n">
+        <v>0.0004763818869832903</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Frequency_234</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>0.2372562289237976</v>
+      </c>
+      <c r="C236" t="n">
+        <v>0.1577596068382263</v>
+      </c>
+      <c r="D236" t="n">
+        <v>-0.0131991496309638</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Frequency_235</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>0.2098465710878372</v>
+      </c>
+      <c r="C237" t="n">
+        <v>0.08469582349061966</v>
+      </c>
+      <c r="D237" t="n">
+        <v>0.002224043244495988</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Frequency_236</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>0.07155168801546097</v>
+      </c>
+      <c r="C238" t="n">
+        <v>0.02622270584106445</v>
+      </c>
+      <c r="D238" t="n">
+        <v>-0.001216345932334661</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Frequency_237</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>-0.01328529603779316</v>
+      </c>
+      <c r="C239" t="n">
+        <v>-0.009027663618326187</v>
+      </c>
+      <c r="D239" t="n">
+        <v>-0.006439994554966688</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Frequency_238</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>0.02159051410853863</v>
+      </c>
+      <c r="C240" t="n">
+        <v>0.03749243542551994</v>
+      </c>
+      <c r="D240" t="n">
+        <v>-0.001817349344491959</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Frequency_239</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>0.03135771676898003</v>
+      </c>
+      <c r="C241" t="n">
+        <v>0.061196468770504</v>
+      </c>
+      <c r="D241" t="n">
+        <v>0.002214032923802733</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Frequency_240</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>-0.1037194281816483</v>
+      </c>
+      <c r="C242" t="n">
+        <v>-0.03808111697435379</v>
+      </c>
+      <c r="D242" t="n">
+        <v>0.0006526639917865396</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Frequency_241</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>0.1325248032808304</v>
+      </c>
+      <c r="C243" t="n">
+        <v>0.1305866688489914</v>
+      </c>
+      <c r="D243" t="n">
+        <v>0.006175453774631023</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Frequency_242</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>0.09356637299060822</v>
+      </c>
+      <c r="C244" t="n">
+        <v>-0.03613848239183426</v>
+      </c>
+      <c r="D244" t="n">
+        <v>-0.01024302467703819</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Frequency_243</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>-0.02089213766157627</v>
+      </c>
+      <c r="C245" t="n">
+        <v>-0.0456584095954895</v>
+      </c>
+      <c r="D245" t="n">
+        <v>5.106777825858444e-05</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Frequency_244</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>0.1215807795524597</v>
+      </c>
+      <c r="C246" t="n">
+        <v>-0.02269876375794411</v>
+      </c>
+      <c r="D246" t="n">
+        <v>0.004685108549892902</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Frequency_245</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>0.07072626799345016</v>
+      </c>
+      <c r="C247" t="n">
+        <v>0.002888326998800039</v>
+      </c>
+      <c r="D247" t="n">
+        <v>0.002684229984879494</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Frequency_246</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>0.2153508514165878</v>
+      </c>
+      <c r="C248" t="n">
+        <v>0.1404782682657242</v>
+      </c>
+      <c r="D248" t="n">
+        <v>-0.001159377512522042</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Frequency_247</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>0.0524711050093174</v>
+      </c>
+      <c r="C249" t="n">
+        <v>0.0128608476370573</v>
+      </c>
+      <c r="D249" t="n">
+        <v>8.405701373703778e-05</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Frequency_248</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>-0.1277680546045303</v>
+      </c>
+      <c r="C250" t="n">
+        <v>-0.05649466440081596</v>
+      </c>
+      <c r="D250" t="n">
+        <v>-0.001893990323878825</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Frequency_249</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>0.04331071302294731</v>
+      </c>
+      <c r="C251" t="n">
+        <v>0.07254599034786224</v>
+      </c>
+      <c r="D251" t="n">
+        <v>-0.004888917785137892</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Frequency_250</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>-0.1586165279150009</v>
+      </c>
+      <c r="C252" t="n">
+        <v>-0.06775608658790588</v>
+      </c>
+      <c r="D252" t="n">
+        <v>0.0007171140168793499</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Frequency_251</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>0.2110785096883774</v>
+      </c>
+      <c r="C253" t="n">
+        <v>0.06552337110042572</v>
+      </c>
+      <c r="D253" t="n">
+        <v>0.009880634024739265</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Frequency_252</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>0.05844555050134659</v>
+      </c>
+      <c r="C254" t="n">
+        <v>-0.06115363538265228</v>
+      </c>
+      <c r="D254" t="n">
+        <v>0.0128869479522109</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Frequency_253</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>0.06899658590555191</v>
+      </c>
+      <c r="C255" t="n">
+        <v>-0.01867418736219406</v>
+      </c>
+      <c r="D255" t="n">
+        <v>0.0008225211640819907</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Frequency_254</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>-0.06845377385616302</v>
+      </c>
+      <c r="C256" t="n">
+        <v>-0.0422651618719101</v>
+      </c>
+      <c r="D256" t="n">
+        <v>0.0002728289109654725</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Frequency_255</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>-0.04222670570015907</v>
+      </c>
+      <c r="C257" t="n">
+        <v>-0.04716194421052933</v>
+      </c>
+      <c r="D257" t="n">
+        <v>0.01166234258562326</v>
       </c>
     </row>
   </sheetData>
